--- a/research/traditional_assets/database/data/south_africa/south_africa_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_chemical_specialty.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1238685724401964</v>
+        <v>0.1235669772946079</v>
       </c>
       <c r="C2">
-        <v>860.1161040537653</v>
+        <v>854.0659783892028</v>
       </c>
       <c r="D2">
-        <v>742.6161040537653</v>
+        <v>745.4961107071035</v>
       </c>
       <c r="E2">
-        <v>-404.5132317900798</v>
+        <v>-395.583099472179</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.930132317900798</v>
       </c>
       <c r="G2">
         <v>117.5</v>
@@ -1451,28 +1451,28 @@
         <v>162.7875</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4491856555904101</v>
       </c>
       <c r="N2">
-        <v>162.7875</v>
+        <v>162.3383143444096</v>
       </c>
       <c r="O2">
-        <v>43.95262499999999</v>
+        <v>43.83134487299058</v>
       </c>
       <c r="P2">
-        <v>118.834875</v>
+        <v>118.506969471419</v>
       </c>
       <c r="Q2">
-        <v>167.634875</v>
+        <v>167.306969471419</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1238685724401964</v>
+        <v>0.124444229590513</v>
       </c>
       <c r="T2">
-        <v>0.9352413814778208</v>
+        <v>0.9421376058058897</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>362.4058292467774</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1235669772946079</v>
+        <v>0.1232653821490194</v>
       </c>
       <c r="C3">
-        <v>854.0659783892028</v>
+        <v>848.0382781229746</v>
       </c>
       <c r="D3">
-        <v>745.4961107071035</v>
+        <v>748.3985427587762</v>
       </c>
       <c r="E3">
-        <v>-395.583099472179</v>
+        <v>-386.6529671542782</v>
       </c>
       <c r="F3">
-        <v>8.930132317900798</v>
+        <v>17.8602646358016</v>
       </c>
       <c r="G3">
         <v>117.5</v>
@@ -1533,28 +1533,28 @@
         <v>162.7875</v>
       </c>
       <c r="M3">
-        <v>0.4491856555904101</v>
+        <v>0.8983713111808203</v>
       </c>
       <c r="N3">
-        <v>162.3383143444096</v>
+        <v>161.8891286888191</v>
       </c>
       <c r="O3">
-        <v>43.83134487299058</v>
+        <v>43.71006474598117</v>
       </c>
       <c r="P3">
-        <v>118.506969471419</v>
+        <v>118.179063942838</v>
       </c>
       <c r="Q3">
-        <v>167.306969471419</v>
+        <v>166.979063942838</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.124444229590513</v>
+        <v>0.1250316348459381</v>
       </c>
       <c r="T3">
-        <v>0.9421376058058897</v>
+        <v>0.9491745694059598</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>362.4058292467774</v>
+        <v>181.2029146233887</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1232653821490194</v>
+        <v>0.1229637870034308</v>
       </c>
       <c r="C4">
-        <v>848.0382781229746</v>
+        <v>842.0332662045115</v>
       </c>
       <c r="D4">
-        <v>748.3985427587762</v>
+        <v>751.3236631582139</v>
       </c>
       <c r="E4">
-        <v>-386.6529671542782</v>
+        <v>-377.7228348363774</v>
       </c>
       <c r="F4">
-        <v>17.8602646358016</v>
+        <v>26.79039695370239</v>
       </c>
       <c r="G4">
         <v>117.5</v>
@@ -1615,28 +1615,28 @@
         <v>162.7875</v>
       </c>
       <c r="M4">
-        <v>0.8983713111808203</v>
+        <v>1.34755696677123</v>
       </c>
       <c r="N4">
-        <v>161.8891286888191</v>
+        <v>161.4399430332287</v>
       </c>
       <c r="O4">
-        <v>43.71006474598117</v>
+        <v>43.58878461897176</v>
       </c>
       <c r="P4">
-        <v>118.179063942838</v>
+        <v>117.851158414257</v>
       </c>
       <c r="Q4">
-        <v>166.979063942838</v>
+        <v>166.651158414257</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1250316348459381</v>
+        <v>0.1256311515499287</v>
       </c>
       <c r="T4">
-        <v>0.9491745694059598</v>
+        <v>0.9563566250390211</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>181.2029146233887</v>
+        <v>120.8019430822592</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1229637870034308</v>
+        <v>0.1226621918578423</v>
       </c>
       <c r="C5">
-        <v>842.0332662045115</v>
+        <v>836.0512097103317</v>
       </c>
       <c r="D5">
-        <v>751.3236631582139</v>
+        <v>754.2717389819348</v>
       </c>
       <c r="E5">
-        <v>-377.7228348363774</v>
+        <v>-368.7927025184766</v>
       </c>
       <c r="F5">
-        <v>26.79039695370239</v>
+        <v>35.72052927160319</v>
       </c>
       <c r="G5">
         <v>117.5</v>
@@ -1697,28 +1697,28 @@
         <v>162.7875</v>
       </c>
       <c r="M5">
-        <v>1.34755696677123</v>
+        <v>1.796742622361641</v>
       </c>
       <c r="N5">
-        <v>161.4399430332287</v>
+        <v>160.9907573776383</v>
       </c>
       <c r="O5">
-        <v>43.58878461897176</v>
+        <v>43.46750449196235</v>
       </c>
       <c r="P5">
-        <v>117.851158414257</v>
+        <v>117.523252885676</v>
       </c>
       <c r="Q5">
-        <v>166.651158414257</v>
+        <v>166.323252885676</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1256311515499287</v>
+        <v>0.1262431581852524</v>
       </c>
       <c r="T5">
-        <v>0.9563566250390211</v>
+        <v>0.9636883068311045</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>120.8019430822592</v>
+        <v>90.60145731169436</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1226621918578423</v>
+        <v>0.1223605967122538</v>
       </c>
       <c r="C6">
-        <v>836.0512097103317</v>
+        <v>830.0923799253322</v>
       </c>
       <c r="D6">
-        <v>754.2717389819348</v>
+        <v>757.2430415148362</v>
       </c>
       <c r="E6">
-        <v>-368.7927025184766</v>
+        <v>-359.8625702005758</v>
       </c>
       <c r="F6">
-        <v>35.72052927160319</v>
+        <v>44.65066158950399</v>
       </c>
       <c r="G6">
         <v>117.5</v>
@@ -1779,28 +1779,28 @@
         <v>162.7875</v>
       </c>
       <c r="M6">
-        <v>1.796742622361641</v>
+        <v>2.24592827795205</v>
       </c>
       <c r="N6">
-        <v>160.9907573776383</v>
+        <v>160.5415717220479</v>
       </c>
       <c r="O6">
-        <v>43.46750449196235</v>
+        <v>43.34622436495294</v>
       </c>
       <c r="P6">
-        <v>117.523252885676</v>
+        <v>117.195347357095</v>
       </c>
       <c r="Q6">
-        <v>166.323252885676</v>
+        <v>165.9953473570949</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1262431581852524</v>
+        <v>0.1268680491707934</v>
       </c>
       <c r="T6">
-        <v>0.9636883068311045</v>
+        <v>0.9711743398188107</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>90.60145731169436</v>
+        <v>72.48116584935549</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1223605967122538</v>
+        <v>0.1220590015666652</v>
       </c>
       <c r="C7">
-        <v>830.0923799253322</v>
+        <v>824.1570524260064</v>
       </c>
       <c r="D7">
-        <v>757.2430415148362</v>
+        <v>760.2378463334112</v>
       </c>
       <c r="E7">
-        <v>-359.8625702005758</v>
+        <v>-350.932437882675</v>
       </c>
       <c r="F7">
-        <v>44.65066158950399</v>
+        <v>53.58079390740479</v>
       </c>
       <c r="G7">
         <v>117.5</v>
@@ -1861,28 +1861,28 @@
         <v>162.7875</v>
       </c>
       <c r="M7">
-        <v>2.24592827795205</v>
+        <v>2.695113933542461</v>
       </c>
       <c r="N7">
-        <v>160.5415717220479</v>
+        <v>160.0923860664575</v>
       </c>
       <c r="O7">
-        <v>43.34622436495294</v>
+        <v>43.22494423794353</v>
       </c>
       <c r="P7">
-        <v>117.195347357095</v>
+        <v>116.867441828514</v>
       </c>
       <c r="Q7">
-        <v>165.9953473570949</v>
+        <v>165.667441828514</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1268680491707934</v>
+        <v>0.1275062357092183</v>
       </c>
       <c r="T7">
-        <v>0.9711743398188107</v>
+        <v>0.9788196501041279</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>72.48116584935549</v>
+        <v>60.40097154112957</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1220590015666652</v>
+        <v>0.1217574064210767</v>
       </c>
       <c r="C8">
-        <v>824.1570524260064</v>
+        <v>818.2455071656441</v>
       </c>
       <c r="D8">
-        <v>760.2378463334112</v>
+        <v>763.2564333909496</v>
       </c>
       <c r="E8">
-        <v>-350.932437882675</v>
+        <v>-342.0023055647742</v>
       </c>
       <c r="F8">
-        <v>53.58079390740478</v>
+        <v>62.51092622530557</v>
       </c>
       <c r="G8">
         <v>117.5</v>
@@ -1943,28 +1943,28 @@
         <v>162.7875</v>
       </c>
       <c r="M8">
-        <v>2.69511393354246</v>
+        <v>3.14429958913287</v>
       </c>
       <c r="N8">
-        <v>160.0923860664575</v>
+        <v>159.6432004108671</v>
       </c>
       <c r="O8">
-        <v>43.22494423794353</v>
+        <v>43.10366411093412</v>
       </c>
       <c r="P8">
-        <v>116.867441828514</v>
+        <v>116.539536299933</v>
       </c>
       <c r="Q8">
-        <v>165.667441828514</v>
+        <v>165.339536299933</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1275062357092183</v>
+        <v>0.1281581466893298</v>
       </c>
       <c r="T8">
-        <v>0.9788196501041279</v>
+        <v>0.9866293756643978</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>60.40097154112959</v>
+        <v>51.77226132096823</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1217574064210767</v>
+        <v>0.1214558112754882</v>
       </c>
       <c r="C9">
-        <v>818.2455071656441</v>
+        <v>812.3580285615698</v>
       </c>
       <c r="D9">
-        <v>763.2564333909497</v>
+        <v>766.2990871047762</v>
       </c>
       <c r="E9">
-        <v>-342.0023055647742</v>
+        <v>-333.0721732468734</v>
       </c>
       <c r="F9">
-        <v>62.51092622530559</v>
+        <v>71.44105854320638</v>
       </c>
       <c r="G9">
         <v>117.5</v>
@@ -2025,28 +2025,28 @@
         <v>162.7875</v>
       </c>
       <c r="M9">
-        <v>3.144299589132871</v>
+        <v>3.593485244723281</v>
       </c>
       <c r="N9">
-        <v>159.6432004108671</v>
+        <v>159.1940147552767</v>
       </c>
       <c r="O9">
-        <v>43.10366411093411</v>
+        <v>42.98238398392471</v>
       </c>
       <c r="P9">
-        <v>116.539536299933</v>
+        <v>116.211630771352</v>
       </c>
       <c r="Q9">
-        <v>165.3395362999329</v>
+        <v>165.011630771352</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1281581466893298</v>
+        <v>0.1288242296472698</v>
       </c>
       <c r="T9">
-        <v>0.9866293756643978</v>
+        <v>0.9946088778672825</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>51.77226132096821</v>
+        <v>45.30072865584719</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1214558112754882</v>
+        <v>0.1211542161298996</v>
       </c>
       <c r="C10">
-        <v>812.3580285615698</v>
+        <v>806.4949055844777</v>
       </c>
       <c r="D10">
-        <v>766.2990871047762</v>
+        <v>769.3660964455848</v>
       </c>
       <c r="E10">
-        <v>-333.0721732468734</v>
+        <v>-324.1420409289726</v>
       </c>
       <c r="F10">
-        <v>71.44105854320638</v>
+        <v>80.37119086110718</v>
       </c>
       <c r="G10">
         <v>117.5</v>
@@ -2107,28 +2107,28 @@
         <v>162.7875</v>
       </c>
       <c r="M10">
-        <v>3.593485244723281</v>
+        <v>4.042670900313691</v>
       </c>
       <c r="N10">
-        <v>159.1940147552767</v>
+        <v>158.7448290996863</v>
       </c>
       <c r="O10">
-        <v>42.98238398392471</v>
+        <v>42.8611038569153</v>
       </c>
       <c r="P10">
-        <v>116.211630771352</v>
+        <v>115.883725242771</v>
       </c>
       <c r="Q10">
-        <v>165.011630771352</v>
+        <v>164.683725242771</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1288242296472698</v>
+        <v>0.1295049517910985</v>
       </c>
       <c r="T10">
-        <v>0.9946088778672825</v>
+        <v>1.002763753744956</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>45.30072865584719</v>
+        <v>40.26731436075305</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1211542161298996</v>
+        <v>0.1208526209843111</v>
       </c>
       <c r="C11">
-        <v>806.4949055844777</v>
+        <v>800.6564318499177</v>
       </c>
       <c r="D11">
-        <v>769.3660964455848</v>
+        <v>772.4577550289257</v>
       </c>
       <c r="E11">
-        <v>-324.1420409289726</v>
+        <v>-315.2119086110718</v>
       </c>
       <c r="F11">
-        <v>80.37119086110718</v>
+        <v>89.30132317900797</v>
       </c>
       <c r="G11">
         <v>117.5</v>
@@ -2189,28 +2189,28 @@
         <v>162.7875</v>
       </c>
       <c r="M11">
-        <v>4.042670900313691</v>
+        <v>4.491856555904101</v>
       </c>
       <c r="N11">
-        <v>158.7448290996863</v>
+        <v>158.2956434440959</v>
       </c>
       <c r="O11">
-        <v>42.8611038569153</v>
+        <v>42.73982372990589</v>
       </c>
       <c r="P11">
-        <v>115.883725242771</v>
+        <v>115.55581971419</v>
       </c>
       <c r="Q11">
-        <v>164.683725242771</v>
+        <v>164.35581971419</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1295049517910985</v>
+        <v>0.130200801093679</v>
       </c>
       <c r="T11">
-        <v>1.002763753744956</v>
+        <v>1.011099849086577</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>40.26731436075305</v>
+        <v>36.24058292467775</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1208526209843111</v>
+        <v>0.1205510258387226</v>
       </c>
       <c r="C12">
-        <v>800.6564318499177</v>
+        <v>794.8429057119988</v>
       </c>
       <c r="D12">
-        <v>772.4577550289257</v>
+        <v>775.5743612089076</v>
       </c>
       <c r="E12">
-        <v>-315.2119086110718</v>
+        <v>-306.281776293171</v>
       </c>
       <c r="F12">
-        <v>89.30132317900798</v>
+        <v>98.23145549690878</v>
       </c>
       <c r="G12">
         <v>117.5</v>
@@ -2271,28 +2271,28 @@
         <v>162.7875</v>
       </c>
       <c r="M12">
-        <v>4.491856555904101</v>
+        <v>4.941042211494511</v>
       </c>
       <c r="N12">
-        <v>158.2956434440959</v>
+        <v>157.8464577885055</v>
       </c>
       <c r="O12">
-        <v>42.73982372990589</v>
+        <v>42.61854360289648</v>
       </c>
       <c r="P12">
-        <v>115.55581971419</v>
+        <v>115.227914185609</v>
       </c>
       <c r="Q12">
-        <v>164.35581971419</v>
+        <v>164.027914185609</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.130200801093679</v>
+        <v>0.1309122874592389</v>
       </c>
       <c r="T12">
-        <v>1.011099849086577</v>
+        <v>1.019623272413404</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>36.24058292467775</v>
+        <v>32.94598447697977</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1205510258387226</v>
+        <v>0.1202494306931341</v>
       </c>
       <c r="C13">
-        <v>794.8429057119988</v>
+        <v>789.054630359367</v>
       </c>
       <c r="D13">
-        <v>775.5743612089076</v>
+        <v>778.7162181741766</v>
       </c>
       <c r="E13">
-        <v>-306.281776293171</v>
+        <v>-297.3516439752702</v>
       </c>
       <c r="F13">
-        <v>98.23145549690878</v>
+        <v>107.1615878148096</v>
       </c>
       <c r="G13">
         <v>117.5</v>
@@ -2353,28 +2353,28 @@
         <v>162.7875</v>
       </c>
       <c r="M13">
-        <v>4.941042211494511</v>
+        <v>5.390227867084921</v>
       </c>
       <c r="N13">
-        <v>157.8464577885055</v>
+        <v>157.397272132915</v>
       </c>
       <c r="O13">
-        <v>42.61854360289648</v>
+        <v>42.49726347588707</v>
       </c>
       <c r="P13">
-        <v>115.227914185609</v>
+        <v>114.900008657028</v>
       </c>
       <c r="Q13">
-        <v>164.027914185609</v>
+        <v>163.700008657028</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1309122874592389</v>
+        <v>0.1316399439694705</v>
       </c>
       <c r="T13">
-        <v>1.019623272413404</v>
+        <v>1.028340409906749</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>32.94598447697977</v>
+        <v>30.2004857705648</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1202494306931341</v>
+        <v>0.1199478355475455</v>
       </c>
       <c r="C14">
-        <v>789.054630359367</v>
+        <v>783.291913913529</v>
       </c>
       <c r="D14">
-        <v>778.7162181741766</v>
+        <v>781.8836340462394</v>
       </c>
       <c r="E14">
-        <v>-297.3516439752702</v>
+        <v>-288.4215116573694</v>
       </c>
       <c r="F14">
-        <v>107.1615878148096</v>
+        <v>116.0917201327104</v>
       </c>
       <c r="G14">
         <v>117.5</v>
@@ -2435,28 +2435,28 @@
         <v>162.7875</v>
       </c>
       <c r="M14">
-        <v>5.390227867084921</v>
+        <v>5.839413522675332</v>
       </c>
       <c r="N14">
-        <v>157.397272132915</v>
+        <v>156.9480864773246</v>
       </c>
       <c r="O14">
-        <v>42.49726347588707</v>
+        <v>42.37598334887765</v>
       </c>
       <c r="P14">
-        <v>114.900008657028</v>
+        <v>114.572103128447</v>
       </c>
       <c r="Q14">
-        <v>163.700008657028</v>
+        <v>163.372103128447</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1316399439694705</v>
+        <v>0.1323843282155696</v>
       </c>
       <c r="T14">
-        <v>1.028340409906749</v>
+        <v>1.037257941365459</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>30.2004857705648</v>
+        <v>27.87737148052134</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1199478355475455</v>
+        <v>0.119646240401957</v>
       </c>
       <c r="C15">
-        <v>783.291913913529</v>
+        <v>777.5550695295825</v>
       </c>
       <c r="D15">
-        <v>781.8836340462394</v>
+        <v>785.0769219801937</v>
       </c>
       <c r="E15">
-        <v>-288.4215116573694</v>
+        <v>-279.4913793394686</v>
       </c>
       <c r="F15">
-        <v>116.0917201327104</v>
+        <v>125.0218524506112</v>
       </c>
       <c r="G15">
         <v>117.5</v>
@@ -2517,28 +2517,28 @@
         <v>162.7875</v>
       </c>
       <c r="M15">
-        <v>5.839413522675332</v>
+        <v>6.288599178265742</v>
       </c>
       <c r="N15">
-        <v>156.9480864773246</v>
+        <v>156.4989008217342</v>
       </c>
       <c r="O15">
-        <v>42.37598334887765</v>
+        <v>42.25470322186824</v>
       </c>
       <c r="P15">
-        <v>114.572103128447</v>
+        <v>114.244197599866</v>
       </c>
       <c r="Q15">
-        <v>163.372103128447</v>
+        <v>163.044197599866</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1323843282155696</v>
+        <v>0.1331460237232058</v>
       </c>
       <c r="T15">
-        <v>1.037257941365459</v>
+        <v>1.046382857276697</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.87737148052134</v>
+        <v>25.8861306604841</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.119646240401957</v>
+        <v>0.1193446452563685</v>
       </c>
       <c r="C16">
-        <v>777.5550695295825</v>
+        <v>771.844415499427</v>
       </c>
       <c r="D16">
-        <v>785.0769219801937</v>
+        <v>788.2964002679389</v>
       </c>
       <c r="E16">
-        <v>-279.4913793394686</v>
+        <v>-270.5612470215678</v>
       </c>
       <c r="F16">
-        <v>125.0218524506112</v>
+        <v>133.951984768512</v>
       </c>
       <c r="G16">
         <v>117.5</v>
@@ -2599,28 +2599,28 @@
         <v>162.7875</v>
       </c>
       <c r="M16">
-        <v>6.288599178265742</v>
+        <v>6.737784833856152</v>
       </c>
       <c r="N16">
-        <v>156.4989008217342</v>
+        <v>156.0497151661438</v>
       </c>
       <c r="O16">
-        <v>42.25470322186824</v>
+        <v>42.13342309485883</v>
       </c>
       <c r="P16">
-        <v>114.244197599866</v>
+        <v>113.916292071285</v>
       </c>
       <c r="Q16">
-        <v>163.044197599866</v>
+        <v>162.716292071285</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1331460237232058</v>
+        <v>0.1339256414780806</v>
       </c>
       <c r="T16">
-        <v>1.046382857276697</v>
+        <v>1.055722477091728</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.8861306604841</v>
+        <v>24.16038861645183</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1193446452563685</v>
+        <v>0.1190430501107799</v>
       </c>
       <c r="C17">
-        <v>771.844415499427</v>
+        <v>766.1602753575231</v>
       </c>
       <c r="D17">
-        <v>788.2964002679389</v>
+        <v>791.5423924439359</v>
       </c>
       <c r="E17">
-        <v>-270.5612470215679</v>
+        <v>-261.631114703667</v>
       </c>
       <c r="F17">
-        <v>133.9519847685119</v>
+        <v>142.8821170864128</v>
       </c>
       <c r="G17">
         <v>117.5</v>
@@ -2681,28 +2681,28 @@
         <v>162.7875</v>
       </c>
       <c r="M17">
-        <v>6.737784833856151</v>
+        <v>7.186970489446562</v>
       </c>
       <c r="N17">
-        <v>156.0497151661438</v>
+        <v>155.6005295105534</v>
       </c>
       <c r="O17">
-        <v>42.13342309485883</v>
+        <v>42.01214296784942</v>
       </c>
       <c r="P17">
-        <v>113.916292071285</v>
+        <v>113.588386542704</v>
       </c>
       <c r="Q17">
-        <v>162.716292071285</v>
+        <v>162.388386542704</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1339256414780806</v>
+        <v>0.1347238215604523</v>
       </c>
       <c r="T17">
-        <v>1.055722477091728</v>
+        <v>1.065284468807118</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>24.16038861645184</v>
+        <v>22.65036432792359</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1190430501107799</v>
+        <v>0.1187414549651914</v>
       </c>
       <c r="C18">
-        <v>766.1602753575231</v>
+        <v>760.5029779892752</v>
       </c>
       <c r="D18">
-        <v>791.5423924439359</v>
+        <v>794.8152273935888</v>
       </c>
       <c r="E18">
-        <v>-261.631114703667</v>
+        <v>-252.7009823857662</v>
       </c>
       <c r="F18">
-        <v>142.8821170864128</v>
+        <v>151.8122494043136</v>
       </c>
       <c r="G18">
         <v>117.5</v>
@@ -2763,28 +2763,28 @@
         <v>162.7875</v>
       </c>
       <c r="M18">
-        <v>7.186970489446562</v>
+        <v>7.636156145036972</v>
       </c>
       <c r="N18">
-        <v>155.6005295105534</v>
+        <v>155.151343854963</v>
       </c>
       <c r="O18">
-        <v>42.01214296784942</v>
+        <v>41.89086284084001</v>
       </c>
       <c r="P18">
-        <v>113.588386542704</v>
+        <v>113.260481014123</v>
       </c>
       <c r="Q18">
-        <v>162.388386542704</v>
+        <v>162.060481014123</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1347238215604523</v>
+        <v>0.135541234897821</v>
       </c>
       <c r="T18">
-        <v>1.065284468807118</v>
+        <v>1.075076869961432</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>22.65036432792359</v>
+        <v>21.31798995569279</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1187414549651914</v>
+        <v>0.1184398598196028</v>
       </c>
       <c r="C19">
-        <v>760.5029779892752</v>
+        <v>754.8728577421175</v>
       </c>
       <c r="D19">
-        <v>794.8152273935888</v>
+        <v>798.1152394643319</v>
       </c>
       <c r="E19">
-        <v>-252.7009823857662</v>
+        <v>-243.7708500678654</v>
       </c>
       <c r="F19">
-        <v>151.8122494043136</v>
+        <v>160.7423817222144</v>
       </c>
       <c r="G19">
         <v>117.5</v>
@@ -2845,28 +2845,28 @@
         <v>162.7875</v>
       </c>
       <c r="M19">
-        <v>7.636156145036972</v>
+        <v>8.085341800627383</v>
       </c>
       <c r="N19">
-        <v>155.151343854963</v>
+        <v>154.7021581993726</v>
       </c>
       <c r="O19">
-        <v>41.89086284084001</v>
+        <v>41.7695827138306</v>
       </c>
       <c r="P19">
-        <v>113.260481014123</v>
+        <v>112.932575485542</v>
       </c>
       <c r="Q19">
-        <v>162.060481014123</v>
+        <v>161.732575485542</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.135541234897821</v>
+        <v>0.1363785851458571</v>
       </c>
       <c r="T19">
-        <v>1.075076869961432</v>
+        <v>1.085108110168291</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>21.31798995569279</v>
+        <v>20.13365718037652</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1184398598196029</v>
+        <v>0.1181382646740143</v>
       </c>
       <c r="C20">
-        <v>754.8728577421173</v>
+        <v>749.2702545393727</v>
       </c>
       <c r="D20">
-        <v>798.1152394643317</v>
+        <v>801.4427685794878</v>
       </c>
       <c r="E20">
-        <v>-243.7708500678654</v>
+        <v>-234.8407177499646</v>
       </c>
       <c r="F20">
-        <v>160.7423817222144</v>
+        <v>169.6725140401151</v>
       </c>
       <c r="G20">
         <v>117.5</v>
@@ -2927,28 +2927,28 @@
         <v>162.7875</v>
       </c>
       <c r="M20">
-        <v>8.085341800627383</v>
+        <v>8.534527456217791</v>
       </c>
       <c r="N20">
-        <v>154.7021581993726</v>
+        <v>154.2529725437822</v>
       </c>
       <c r="O20">
-        <v>41.7695827138306</v>
+        <v>41.64830258682119</v>
       </c>
       <c r="P20">
-        <v>112.932575485542</v>
+        <v>112.604669956961</v>
       </c>
       <c r="Q20">
-        <v>161.732575485542</v>
+        <v>161.404669956961</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1363785851458571</v>
+        <v>0.1372366107086597</v>
       </c>
       <c r="T20">
-        <v>1.085108110168291</v>
+        <v>1.095387035318529</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>20.13365718037652</v>
+        <v>19.07399101298829</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1181382646740143</v>
+        <v>0.1178366695284258</v>
       </c>
       <c r="C21">
-        <v>749.2702545393727</v>
+        <v>743.695513996979</v>
       </c>
       <c r="D21">
-        <v>801.4427685794878</v>
+        <v>804.7981603549949</v>
       </c>
       <c r="E21">
-        <v>-234.8407177499646</v>
+        <v>-225.9105854320638</v>
       </c>
       <c r="F21">
-        <v>169.6725140401151</v>
+        <v>178.602646358016</v>
       </c>
       <c r="G21">
         <v>117.5</v>
@@ -3009,28 +3009,28 @@
         <v>162.7875</v>
       </c>
       <c r="M21">
-        <v>8.534527456217791</v>
+        <v>8.983713111808202</v>
       </c>
       <c r="N21">
-        <v>154.2529725437822</v>
+        <v>153.8037868881918</v>
       </c>
       <c r="O21">
-        <v>41.64830258682119</v>
+        <v>41.52702245981177</v>
       </c>
       <c r="P21">
-        <v>112.604669956961</v>
+        <v>112.27676442838</v>
       </c>
       <c r="Q21">
-        <v>161.404669956961</v>
+        <v>161.07676442838</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1372366107086597</v>
+        <v>0.1381160869105323</v>
       </c>
       <c r="T21">
-        <v>1.095387035318529</v>
+        <v>1.105922933597523</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>19.07399101298829</v>
+        <v>18.12029146233887</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1178366695284258</v>
+        <v>0.1175350743828373</v>
       </c>
       <c r="C22">
-        <v>743.695513996979</v>
+        <v>738.1489875431536</v>
       </c>
       <c r="D22">
-        <v>804.7981603549949</v>
+        <v>808.1817662190704</v>
       </c>
       <c r="E22">
-        <v>-225.9105854320638</v>
+        <v>-216.980453114163</v>
       </c>
       <c r="F22">
-        <v>178.602646358016</v>
+        <v>187.5327786759168</v>
       </c>
       <c r="G22">
         <v>117.5</v>
@@ -3091,28 +3091,28 @@
         <v>162.7875</v>
       </c>
       <c r="M22">
-        <v>8.983713111808202</v>
+        <v>9.432898767398614</v>
       </c>
       <c r="N22">
-        <v>153.8037868881918</v>
+        <v>153.3546012326013</v>
       </c>
       <c r="O22">
-        <v>41.52702245981177</v>
+        <v>41.40574233280236</v>
       </c>
       <c r="P22">
-        <v>112.27676442838</v>
+        <v>111.948858899799</v>
       </c>
       <c r="Q22">
-        <v>161.07676442838</v>
+        <v>160.748858899799</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1381160869105323</v>
+        <v>0.1390178283327054</v>
       </c>
       <c r="T22">
-        <v>1.105922933597523</v>
+        <v>1.116725563478517</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>18.12029146233887</v>
+        <v>17.25742044032273</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1175350743828373</v>
+        <v>0.1172334792372487</v>
       </c>
       <c r="C23">
-        <v>738.1489875431537</v>
+        <v>732.6310325410923</v>
       </c>
       <c r="D23">
-        <v>808.1817662190704</v>
+        <v>811.5939435349098</v>
       </c>
       <c r="E23">
-        <v>-216.980453114163</v>
+        <v>-208.0503207962622</v>
       </c>
       <c r="F23">
-        <v>187.5327786759167</v>
+        <v>196.4629109938176</v>
       </c>
       <c r="G23">
         <v>117.5</v>
@@ -3173,28 +3173,28 @@
         <v>162.7875</v>
       </c>
       <c r="M23">
-        <v>9.432898767398612</v>
+        <v>9.882084422989022</v>
       </c>
       <c r="N23">
-        <v>153.3546012326013</v>
+        <v>152.905415577011</v>
       </c>
       <c r="O23">
-        <v>41.40574233280236</v>
+        <v>41.28446220579296</v>
       </c>
       <c r="P23">
-        <v>111.948858899799</v>
+        <v>111.620953371218</v>
       </c>
       <c r="Q23">
-        <v>160.748858899799</v>
+        <v>160.420953371218</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1390178283327054</v>
+        <v>0.1399426913298061</v>
       </c>
       <c r="T23">
-        <v>1.116725563478517</v>
+        <v>1.12780518386928</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>17.25742044032274</v>
+        <v>16.47299223848989</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1172334792372487</v>
+        <v>0.1169318840916602</v>
       </c>
       <c r="C24">
-        <v>732.6310325410923</v>
+        <v>727.1420124147902</v>
       </c>
       <c r="D24">
-        <v>811.5939435349098</v>
+        <v>815.0350557265085</v>
       </c>
       <c r="E24">
-        <v>-208.0503207962622</v>
+        <v>-199.1201884783614</v>
       </c>
       <c r="F24">
-        <v>196.4629109938176</v>
+        <v>205.3930433117183</v>
       </c>
       <c r="G24">
         <v>117.5</v>
@@ -3255,28 +3255,28 @@
         <v>162.7875</v>
       </c>
       <c r="M24">
-        <v>9.882084422989022</v>
+        <v>10.33127007857943</v>
       </c>
       <c r="N24">
-        <v>152.905415577011</v>
+        <v>152.4562299214205</v>
       </c>
       <c r="O24">
-        <v>41.28446220579296</v>
+        <v>41.16318207878355</v>
       </c>
       <c r="P24">
-        <v>111.620953371218</v>
+        <v>111.293047842637</v>
       </c>
       <c r="Q24">
-        <v>160.420953371218</v>
+        <v>160.093047842637</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1399426913298061</v>
+        <v>0.1408915767424158</v>
       </c>
       <c r="T24">
-        <v>1.12780518386928</v>
+        <v>1.139172586607855</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.47299223848989</v>
+        <v>15.7567751846425</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1169318840916602</v>
+        <v>0.1166302889460717</v>
       </c>
       <c r="C25">
-        <v>727.1420124147902</v>
+        <v>721.682296778074</v>
       </c>
       <c r="D25">
-        <v>815.0350557265085</v>
+        <v>818.5054724076932</v>
       </c>
       <c r="E25">
-        <v>-199.1201884783614</v>
+        <v>-190.1900561604606</v>
       </c>
       <c r="F25">
-        <v>205.3930433117183</v>
+        <v>214.3231756296192</v>
       </c>
       <c r="G25">
         <v>117.5</v>
@@ -3337,28 +3337,28 @@
         <v>162.7875</v>
       </c>
       <c r="M25">
-        <v>10.33127007857943</v>
+        <v>10.78045573416984</v>
       </c>
       <c r="N25">
-        <v>152.4562299214205</v>
+        <v>152.0070442658301</v>
       </c>
       <c r="O25">
-        <v>41.16318207878355</v>
+        <v>41.04190195177414</v>
       </c>
       <c r="P25">
-        <v>111.293047842637</v>
+        <v>110.965142314056</v>
       </c>
       <c r="Q25">
-        <v>160.093047842637</v>
+        <v>159.765142314056</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1408915767424158</v>
+        <v>0.1418654328237785</v>
       </c>
       <c r="T25">
-        <v>1.139172586607855</v>
+        <v>1.15083913152376</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.7567751846425</v>
+        <v>15.10024288528239</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1166302889460717</v>
+        <v>0.1163286938004831</v>
       </c>
       <c r="C26">
-        <v>721.682296778074</v>
+        <v>716.25226156695</v>
       </c>
       <c r="D26">
-        <v>818.5054724076932</v>
+        <v>822.0055695144699</v>
       </c>
       <c r="E26">
-        <v>-190.1900561604606</v>
+        <v>-181.2599238425598</v>
       </c>
       <c r="F26">
-        <v>214.3231756296191</v>
+        <v>223.2533079475199</v>
       </c>
       <c r="G26">
         <v>117.5</v>
@@ -3419,28 +3419,28 @@
         <v>162.7875</v>
       </c>
       <c r="M26">
-        <v>10.78045573416984</v>
+        <v>11.22964138976025</v>
       </c>
       <c r="N26">
-        <v>152.0070442658301</v>
+        <v>151.5578586102397</v>
       </c>
       <c r="O26">
-        <v>41.04190195177414</v>
+        <v>40.92062182476473</v>
       </c>
       <c r="P26">
-        <v>110.965142314056</v>
+        <v>110.637236785475</v>
       </c>
       <c r="Q26">
-        <v>159.765142314056</v>
+        <v>159.437236785475</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1418654328237785</v>
+        <v>0.1428652584006442</v>
       </c>
       <c r="T26">
-        <v>1.15083913152376</v>
+        <v>1.162816784304091</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>15.1002428852824</v>
+        <v>14.4962331698711</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1163286938004831</v>
+        <v>0.1160270986548946</v>
       </c>
       <c r="C27">
-        <v>716.25226156695</v>
+        <v>710.8522891753557</v>
       </c>
       <c r="D27">
-        <v>822.0055695144699</v>
+        <v>825.5357294407764</v>
       </c>
       <c r="E27">
-        <v>-181.2599238425598</v>
+        <v>-172.329791524659</v>
       </c>
       <c r="F27">
-        <v>223.2533079475199</v>
+        <v>232.1834402654208</v>
       </c>
       <c r="G27">
         <v>117.5</v>
@@ -3501,28 +3501,28 @@
         <v>162.7875</v>
       </c>
       <c r="M27">
-        <v>11.22964138976025</v>
+        <v>11.67882704535066</v>
       </c>
       <c r="N27">
-        <v>151.5578586102397</v>
+        <v>151.1086729546493</v>
       </c>
       <c r="O27">
-        <v>40.92062182476473</v>
+        <v>40.79934169775532</v>
       </c>
       <c r="P27">
-        <v>110.637236785475</v>
+        <v>110.309331256894</v>
       </c>
       <c r="Q27">
-        <v>159.437236785475</v>
+        <v>159.109331256894</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1428652584006442</v>
+        <v>0.1438921062903981</v>
       </c>
       <c r="T27">
-        <v>1.162816784304091</v>
+        <v>1.175118157429835</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.4962331698711</v>
+        <v>13.93868574026067</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1160270986548946</v>
+        <v>0.1157255035093061</v>
       </c>
       <c r="C28">
-        <v>710.8522891753557</v>
+        <v>705.4827685944316</v>
       </c>
       <c r="D28">
-        <v>825.5357294407764</v>
+        <v>829.0963411777532</v>
       </c>
       <c r="E28">
-        <v>-172.329791524659</v>
+        <v>-163.3996592067582</v>
       </c>
       <c r="F28">
-        <v>232.1834402654208</v>
+        <v>241.1135725833215</v>
       </c>
       <c r="G28">
         <v>117.5</v>
@@ -3583,28 +3583,28 @@
         <v>162.7875</v>
       </c>
       <c r="M28">
-        <v>11.67882704535066</v>
+        <v>12.12801270094107</v>
       </c>
       <c r="N28">
-        <v>151.1086729546493</v>
+        <v>150.6594872990589</v>
       </c>
       <c r="O28">
-        <v>40.79934169775532</v>
+        <v>40.6780615707459</v>
       </c>
       <c r="P28">
-        <v>110.309331256894</v>
+        <v>109.981425728313</v>
       </c>
       <c r="Q28">
-        <v>159.109331256894</v>
+        <v>158.781425728313</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1438921062903981</v>
+        <v>0.1449470869990495</v>
       </c>
       <c r="T28">
-        <v>1.175118157429835</v>
+        <v>1.187756554476832</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.93868574026067</v>
+        <v>13.42243812025102</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1157255035093061</v>
+        <v>0.1154239083637176</v>
       </c>
       <c r="C29">
-        <v>705.4827685944316</v>
+        <v>700.1440955554059</v>
       </c>
       <c r="D29">
-        <v>829.0963411777532</v>
+        <v>832.6878004566282</v>
       </c>
       <c r="E29">
-        <v>-163.3996592067582</v>
+        <v>-154.4695268888574</v>
       </c>
       <c r="F29">
-        <v>241.1135725833215</v>
+        <v>250.0437049012224</v>
       </c>
       <c r="G29">
         <v>117.5</v>
@@ -3665,28 +3665,28 @@
         <v>162.7875</v>
       </c>
       <c r="M29">
-        <v>12.12801270094107</v>
+        <v>12.57719835653148</v>
       </c>
       <c r="N29">
-        <v>150.6594872990589</v>
+        <v>150.2103016434685</v>
       </c>
       <c r="O29">
-        <v>40.6780615707459</v>
+        <v>40.55678144373649</v>
       </c>
       <c r="P29">
-        <v>109.981425728313</v>
+        <v>109.653520199732</v>
       </c>
       <c r="Q29">
-        <v>158.781425728313</v>
+        <v>158.453520199732</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1449470869990495</v>
+        <v>0.1460313727273855</v>
       </c>
       <c r="T29">
-        <v>1.187756554476832</v>
+        <v>1.200746018108469</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>13.42243812025102</v>
+        <v>12.94306533024205</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1154239083637176</v>
+        <v>0.115439863218129</v>
       </c>
       <c r="C30">
-        <v>700.1440955554059</v>
+        <v>691.0231901369768</v>
       </c>
       <c r="D30">
-        <v>832.6878004566282</v>
+        <v>832.4970273561</v>
       </c>
       <c r="E30">
-        <v>-154.4695268888574</v>
+        <v>-145.5393945709566</v>
       </c>
       <c r="F30">
-        <v>250.0437049012224</v>
+        <v>258.9738372191231</v>
       </c>
       <c r="G30">
         <v>117.5</v>
@@ -3747,45 +3747,45 @@
         <v>162.7875</v>
       </c>
       <c r="M30">
-        <v>12.57719835653148</v>
+        <v>13.41484476795058</v>
       </c>
       <c r="N30">
-        <v>150.2103016434685</v>
+        <v>149.3726552320494</v>
       </c>
       <c r="O30">
-        <v>40.55678144373649</v>
+        <v>40.33061691265334</v>
       </c>
       <c r="P30">
-        <v>109.653520199732</v>
+        <v>109.0420383193961</v>
       </c>
       <c r="Q30">
-        <v>158.453520199732</v>
+        <v>157.8420383193961</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1460313727273855</v>
+        <v>0.1471462017156747</v>
       </c>
       <c r="T30">
-        <v>1.200746018108469</v>
+        <v>1.214101382124095</v>
       </c>
       <c r="U30">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V30">
         <v>0.27</v>
       </c>
       <c r="W30">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y30">
-        <v>12.94306533024205</v>
+        <v>12.13487765351678</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.115439863218129</v>
+        <v>0.1151492180725405</v>
       </c>
       <c r="C31">
-        <v>691.0231901369768</v>
+        <v>685.5820837438505</v>
       </c>
       <c r="D31">
-        <v>832.4970273561</v>
+        <v>835.9860532808744</v>
       </c>
       <c r="E31">
-        <v>-145.5393945709566</v>
+        <v>-136.6092622530559</v>
       </c>
       <c r="F31">
-        <v>258.9738372191231</v>
+        <v>267.9039695370239</v>
       </c>
       <c r="G31">
         <v>117.5</v>
@@ -3829,28 +3829,28 @@
         <v>162.7875</v>
       </c>
       <c r="M31">
-        <v>13.41484476795058</v>
+        <v>13.87742562201784</v>
       </c>
       <c r="N31">
-        <v>149.3726552320494</v>
+        <v>148.9100743779821</v>
       </c>
       <c r="O31">
-        <v>40.33061691265334</v>
+        <v>40.20572008205518</v>
       </c>
       <c r="P31">
-        <v>109.0420383193961</v>
+        <v>108.704354295927</v>
       </c>
       <c r="Q31">
-        <v>157.8420383193961</v>
+        <v>157.504354295927</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1471462017156747</v>
+        <v>0.1482928829607721</v>
       </c>
       <c r="T31">
-        <v>1.214101382124095</v>
+        <v>1.227838327968739</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>12.13487765351678</v>
+        <v>11.73038173173289</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1151492180725405</v>
+        <v>0.114858572926952</v>
       </c>
       <c r="C32">
-        <v>685.5820837438505</v>
+        <v>680.1703457087682</v>
       </c>
       <c r="D32">
-        <v>835.9860532808744</v>
+        <v>839.5044475636929</v>
       </c>
       <c r="E32">
-        <v>-136.6092622530559</v>
+        <v>-127.6791299351551</v>
       </c>
       <c r="F32">
-        <v>267.9039695370239</v>
+        <v>276.8341018549247</v>
       </c>
       <c r="G32">
         <v>117.5</v>
@@ -3911,28 +3911,28 @@
         <v>162.7875</v>
       </c>
       <c r="M32">
-        <v>13.87742562201784</v>
+        <v>14.3400064760851</v>
       </c>
       <c r="N32">
-        <v>148.9100743779821</v>
+        <v>148.4474935239149</v>
       </c>
       <c r="O32">
-        <v>40.20572008205518</v>
+        <v>40.08082325145701</v>
       </c>
       <c r="P32">
-        <v>108.704354295927</v>
+        <v>108.3666702724578</v>
       </c>
       <c r="Q32">
-        <v>157.504354295927</v>
+        <v>157.1666702724578</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1482928829607721</v>
+        <v>0.1494728013434087</v>
       </c>
       <c r="T32">
-        <v>1.227838327968739</v>
+        <v>1.241973446156706</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.73038173173289</v>
+        <v>11.35198232103183</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.114858572926952</v>
+        <v>0.1145679277813634</v>
       </c>
       <c r="C33">
-        <v>680.1703457087682</v>
+        <v>674.7883484046215</v>
       </c>
       <c r="D33">
-        <v>839.5044475636929</v>
+        <v>843.0525825774471</v>
       </c>
       <c r="E33">
-        <v>-127.6791299351551</v>
+        <v>-118.7489976172542</v>
       </c>
       <c r="F33">
-        <v>276.8341018549247</v>
+        <v>285.7642341728255</v>
       </c>
       <c r="G33">
         <v>117.5</v>
@@ -3993,28 +3993,28 @@
         <v>162.7875</v>
       </c>
       <c r="M33">
-        <v>14.3400064760851</v>
+        <v>14.80258733015236</v>
       </c>
       <c r="N33">
-        <v>148.4474935239149</v>
+        <v>147.9849126698476</v>
       </c>
       <c r="O33">
-        <v>40.08082325145701</v>
+        <v>39.95592642085886</v>
       </c>
       <c r="P33">
-        <v>108.3666702724578</v>
+        <v>108.0289862489887</v>
       </c>
       <c r="Q33">
-        <v>157.1666702724578</v>
+        <v>156.8289862489887</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1494728013434087</v>
+        <v>0.1506874232078874</v>
       </c>
       <c r="T33">
-        <v>1.241973446156706</v>
+        <v>1.256524303114907</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.35198232103183</v>
+        <v>10.99723287349958</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1145679277813634</v>
+        <v>0.1142772826357749</v>
       </c>
       <c r="C34">
-        <v>674.7883484046215</v>
+        <v>669.4364705263033</v>
       </c>
       <c r="D34">
-        <v>843.0525825774471</v>
+        <v>846.6308370170296</v>
       </c>
       <c r="E34">
-        <v>-118.7489976172542</v>
+        <v>-109.8188652993534</v>
       </c>
       <c r="F34">
-        <v>285.7642341728255</v>
+        <v>294.6943664907263</v>
       </c>
       <c r="G34">
         <v>117.5</v>
@@ -4075,28 +4075,28 @@
         <v>162.7875</v>
       </c>
       <c r="M34">
-        <v>14.80258733015236</v>
+        <v>15.26516818421962</v>
       </c>
       <c r="N34">
-        <v>147.9849126698476</v>
+        <v>147.5223318157803</v>
       </c>
       <c r="O34">
-        <v>39.95592642085886</v>
+        <v>39.8310295902607</v>
       </c>
       <c r="P34">
-        <v>108.0289862489887</v>
+        <v>107.6913022255196</v>
       </c>
       <c r="Q34">
-        <v>156.8289862489887</v>
+        <v>156.4913022255196</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1506874232078874</v>
+        <v>0.1519383024414551</v>
       </c>
       <c r="T34">
-        <v>1.256524303114907</v>
+        <v>1.27150951401216</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.99723287349958</v>
+        <v>10.66398339248444</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1142772826357749</v>
+        <v>0.1139866374901864</v>
       </c>
       <c r="C35">
-        <v>669.4364705263033</v>
+        <v>664.1150972254457</v>
       </c>
       <c r="D35">
-        <v>846.6308370170296</v>
+        <v>850.2395960340727</v>
       </c>
       <c r="E35">
-        <v>-109.8188652993534</v>
+        <v>-100.8887329814526</v>
       </c>
       <c r="F35">
-        <v>294.6943664907263</v>
+        <v>303.6244988086272</v>
       </c>
       <c r="G35">
         <v>117.5</v>
@@ -4157,28 +4157,28 @@
         <v>162.7875</v>
       </c>
       <c r="M35">
-        <v>15.26516818421962</v>
+        <v>15.72774903828689</v>
       </c>
       <c r="N35">
-        <v>147.5223318157803</v>
+        <v>147.0597509617131</v>
       </c>
       <c r="O35">
-        <v>39.8310295902607</v>
+        <v>39.70613275966254</v>
       </c>
       <c r="P35">
-        <v>107.6913022255196</v>
+        <v>107.3536182020506</v>
       </c>
       <c r="Q35">
-        <v>156.4913022255196</v>
+        <v>156.1536182020506</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1519383024414551</v>
+        <v>0.153227087106343</v>
       </c>
       <c r="T35">
-        <v>1.27150951401216</v>
+        <v>1.286948822209328</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.66398339248444</v>
+        <v>10.35033682211725</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1139866374901864</v>
+        <v>0.1136959923445978</v>
       </c>
       <c r="C36">
-        <v>664.1150972254457</v>
+        <v>658.8246202486174</v>
       </c>
       <c r="D36">
-        <v>850.2395960340727</v>
+        <v>853.8792513751454</v>
       </c>
       <c r="E36">
-        <v>-100.8887329814526</v>
+        <v>-91.95860066355181</v>
       </c>
       <c r="F36">
-        <v>303.6244988086272</v>
+        <v>312.554631126528</v>
       </c>
       <c r="G36">
         <v>117.5</v>
@@ -4239,28 +4239,28 @@
         <v>162.7875</v>
       </c>
       <c r="M36">
-        <v>15.72774903828689</v>
+        <v>16.19032989235415</v>
       </c>
       <c r="N36">
-        <v>147.0597509617131</v>
+        <v>146.5971701076458</v>
       </c>
       <c r="O36">
-        <v>39.70613275966254</v>
+        <v>39.58123592906437</v>
       </c>
       <c r="P36">
-        <v>107.3536182020506</v>
+        <v>107.0159341785814</v>
       </c>
       <c r="Q36">
-        <v>156.1536182020506</v>
+        <v>155.8159341785814</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.153227087106343</v>
+        <v>0.1545555266839967</v>
       </c>
       <c r="T36">
-        <v>1.286948822209328</v>
+        <v>1.302863186043334</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.35033682211725</v>
+        <v>10.0546129129139</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1136959923445978</v>
+        <v>0.1138521071990093</v>
       </c>
       <c r="C37">
-        <v>658.8246202486174</v>
+        <v>647.9356472643497</v>
       </c>
       <c r="D37">
-        <v>853.8792513751454</v>
+        <v>851.9204107087784</v>
       </c>
       <c r="E37">
-        <v>-91.95860066355181</v>
+        <v>-83.02846834565099</v>
       </c>
       <c r="F37">
-        <v>312.554631126528</v>
+        <v>321.4847634444288</v>
       </c>
       <c r="G37">
         <v>117.5</v>
@@ -4321,45 +4321,45 @@
         <v>162.7875</v>
       </c>
       <c r="M37">
-        <v>16.19032989235415</v>
+        <v>17.19943484427694</v>
       </c>
       <c r="N37">
-        <v>146.5971701076458</v>
+        <v>145.588065155723</v>
       </c>
       <c r="O37">
-        <v>39.58123592906437</v>
+        <v>39.30877759204522</v>
       </c>
       <c r="P37">
-        <v>107.0159341785814</v>
+        <v>106.2792875636778</v>
       </c>
       <c r="Q37">
-        <v>155.8159341785814</v>
+        <v>155.0792875636778</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1545555266839967</v>
+        <v>0.155925479998452</v>
       </c>
       <c r="T37">
-        <v>1.302863186043334</v>
+        <v>1.319274873747151</v>
       </c>
       <c r="U37">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V37">
         <v>0.27</v>
       </c>
       <c r="W37">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>10.0546129129139</v>
+        <v>9.464700524980739</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1138521071990093</v>
+        <v>0.1135738720534208</v>
       </c>
       <c r="C38">
-        <v>647.9356472643493</v>
+        <v>642.5029423815608</v>
       </c>
       <c r="D38">
-        <v>851.920410708778</v>
+        <v>855.4178381438903</v>
       </c>
       <c r="E38">
-        <v>-83.02846834565105</v>
+        <v>-74.09833602775024</v>
       </c>
       <c r="F38">
-        <v>321.4847634444287</v>
+        <v>330.4148957623295</v>
       </c>
       <c r="G38">
         <v>117.5</v>
@@ -4403,28 +4403,28 @@
         <v>162.7875</v>
       </c>
       <c r="M38">
-        <v>17.19943484427694</v>
+        <v>17.67719692328463</v>
       </c>
       <c r="N38">
-        <v>145.588065155723</v>
+        <v>145.1103030767153</v>
       </c>
       <c r="O38">
-        <v>39.30877759204522</v>
+        <v>39.17978183071314</v>
       </c>
       <c r="P38">
-        <v>106.2792875636778</v>
+        <v>105.9305212460022</v>
       </c>
       <c r="Q38">
-        <v>155.0792875636778</v>
+        <v>154.7305212460022</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.155925479998452</v>
+        <v>0.1573389238943187</v>
       </c>
       <c r="T38">
-        <v>1.319274873747151</v>
+        <v>1.33620756740982</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.46470052498074</v>
+        <v>9.208897808089368</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1135738720534208</v>
+        <v>0.1132956369078323</v>
       </c>
       <c r="C39">
-        <v>642.5029423815608</v>
+        <v>637.0990721694607</v>
       </c>
       <c r="D39">
-        <v>855.4178381438903</v>
+        <v>858.944100249691</v>
       </c>
       <c r="E39">
-        <v>-74.09833602775024</v>
+        <v>-65.16820370984948</v>
       </c>
       <c r="F39">
-        <v>330.4148957623295</v>
+        <v>339.3450280802303</v>
       </c>
       <c r="G39">
         <v>117.5</v>
@@ -4485,28 +4485,28 @@
         <v>162.7875</v>
       </c>
       <c r="M39">
-        <v>17.67719692328463</v>
+        <v>18.15495900229232</v>
       </c>
       <c r="N39">
-        <v>145.1103030767153</v>
+        <v>144.6325409977077</v>
       </c>
       <c r="O39">
-        <v>39.17978183071314</v>
+        <v>39.05078606938107</v>
       </c>
       <c r="P39">
-        <v>105.9305212460022</v>
+        <v>105.5817549283266</v>
       </c>
       <c r="Q39">
-        <v>154.7305212460022</v>
+        <v>154.3817549283266</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1573389238943187</v>
+        <v>0.1587979627545681</v>
       </c>
       <c r="T39">
-        <v>1.33620756740982</v>
+        <v>1.353686476997091</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.208897808089368</v>
+        <v>8.96655839208702</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1132956369078323</v>
+        <v>0.1130174017622437</v>
       </c>
       <c r="C40">
-        <v>637.0990721694607</v>
+        <v>631.7243946968797</v>
       </c>
       <c r="D40">
-        <v>858.944100249691</v>
+        <v>862.4995550950108</v>
       </c>
       <c r="E40">
-        <v>-65.16820370984948</v>
+        <v>-56.23807139194867</v>
       </c>
       <c r="F40">
-        <v>339.3450280802303</v>
+        <v>348.2751603981311</v>
       </c>
       <c r="G40">
         <v>117.5</v>
@@ -4567,28 +4567,28 @@
         <v>162.7875</v>
       </c>
       <c r="M40">
-        <v>18.15495900229232</v>
+        <v>18.63272108130001</v>
       </c>
       <c r="N40">
-        <v>144.6325409977077</v>
+        <v>144.1547789186999</v>
       </c>
       <c r="O40">
-        <v>39.05078606938107</v>
+        <v>38.92179030804899</v>
       </c>
       <c r="P40">
-        <v>105.5817549283266</v>
+        <v>105.2329886106509</v>
       </c>
       <c r="Q40">
-        <v>154.3817549283266</v>
+        <v>154.0329886106509</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1587979627545681</v>
+        <v>0.1603048389544979</v>
       </c>
       <c r="T40">
-        <v>1.353686476997091</v>
+        <v>1.371738465587223</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.96655839208702</v>
+        <v>8.736646638443762</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1130174017622437</v>
+        <v>0.1127391666166552</v>
       </c>
       <c r="C41">
-        <v>631.7243946968797</v>
+        <v>626.379273985953</v>
       </c>
       <c r="D41">
-        <v>862.4995550950108</v>
+        <v>866.084566701985</v>
       </c>
       <c r="E41">
-        <v>-56.23807139194867</v>
+        <v>-47.30793907404785</v>
       </c>
       <c r="F41">
-        <v>348.2751603981311</v>
+        <v>357.2052927160319</v>
       </c>
       <c r="G41">
         <v>117.5</v>
@@ -4649,28 +4649,28 @@
         <v>162.7875</v>
       </c>
       <c r="M41">
-        <v>18.63272108130001</v>
+        <v>19.11048316030771</v>
       </c>
       <c r="N41">
-        <v>144.1547789186999</v>
+        <v>143.6770168396923</v>
       </c>
       <c r="O41">
-        <v>38.92179030804899</v>
+        <v>38.79279454671691</v>
       </c>
       <c r="P41">
-        <v>105.2329886106509</v>
+        <v>104.8842222929754</v>
       </c>
       <c r="Q41">
-        <v>154.0329886106509</v>
+        <v>153.6842222929753</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1603048389544979</v>
+        <v>0.161861944361092</v>
       </c>
       <c r="T41">
-        <v>1.371738465587223</v>
+        <v>1.39039218713036</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.736646638443762</v>
+        <v>8.518230472482667</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1127391666166552</v>
+        <v>0.1124609314710667</v>
       </c>
       <c r="C42">
-        <v>626.379273985953</v>
+        <v>621.0640801363651</v>
       </c>
       <c r="D42">
-        <v>866.084566701985</v>
+        <v>869.6995051702978</v>
       </c>
       <c r="E42">
-        <v>-47.30793907404785</v>
+        <v>-38.37780675614704</v>
       </c>
       <c r="F42">
-        <v>357.2052927160319</v>
+        <v>366.1354250339327</v>
       </c>
       <c r="G42">
         <v>117.5</v>
@@ -4731,28 +4731,28 @@
         <v>162.7875</v>
       </c>
       <c r="M42">
-        <v>19.11048316030771</v>
+        <v>19.5882452393154</v>
       </c>
       <c r="N42">
-        <v>143.6770168396923</v>
+        <v>143.1992547606846</v>
       </c>
       <c r="O42">
-        <v>38.79279454671691</v>
+        <v>38.66379878538483</v>
       </c>
       <c r="P42">
-        <v>104.8842222929754</v>
+        <v>104.5354559752997</v>
       </c>
       <c r="Q42">
-        <v>153.6842222929753</v>
+        <v>153.3354559752997</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.161861944361092</v>
+        <v>0.1634718330018079</v>
       </c>
       <c r="T42">
-        <v>1.39039218713036</v>
+        <v>1.409678238217332</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.518230472482667</v>
+        <v>8.310468753641626</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1124609314710667</v>
+        <v>0.1121826963254781</v>
       </c>
       <c r="C43">
-        <v>621.0640801363651</v>
+        <v>615.7791894527131</v>
       </c>
       <c r="D43">
-        <v>869.6995051702978</v>
+        <v>873.3447468045466</v>
       </c>
       <c r="E43">
-        <v>-38.37780675614704</v>
+        <v>-29.44767443824622</v>
       </c>
       <c r="F43">
-        <v>366.1354250339327</v>
+        <v>375.0655573518335</v>
       </c>
       <c r="G43">
         <v>117.5</v>
@@ -4813,28 +4813,28 @@
         <v>162.7875</v>
       </c>
       <c r="M43">
-        <v>19.5882452393154</v>
+        <v>20.06600731832309</v>
       </c>
       <c r="N43">
-        <v>143.1992547606846</v>
+        <v>142.7214926816769</v>
       </c>
       <c r="O43">
-        <v>38.66379878538483</v>
+        <v>38.53480302405276</v>
       </c>
       <c r="P43">
-        <v>104.5354559752997</v>
+        <v>104.1866896576241</v>
       </c>
       <c r="Q43">
-        <v>153.3354559752997</v>
+        <v>152.9866896576241</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1634718330018079</v>
+        <v>0.1651372350439278</v>
       </c>
       <c r="T43">
-        <v>1.409678238217332</v>
+        <v>1.429629325548683</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.310468753641626</v>
+        <v>8.112600449983491</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1121826963254781</v>
+        <v>0.1119044611798896</v>
       </c>
       <c r="C44">
-        <v>615.7791894527131</v>
+        <v>610.5249845750932</v>
       </c>
       <c r="D44">
-        <v>873.3447468045466</v>
+        <v>877.0206742448274</v>
       </c>
       <c r="E44">
-        <v>-29.44767443824628</v>
+        <v>-20.51754212034547</v>
       </c>
       <c r="F44">
-        <v>375.0655573518335</v>
+        <v>383.9956896697343</v>
       </c>
       <c r="G44">
         <v>117.5</v>
@@ -4895,28 +4895,28 @@
         <v>162.7875</v>
       </c>
       <c r="M44">
-        <v>20.06600731832309</v>
+        <v>20.54376939733078</v>
       </c>
       <c r="N44">
-        <v>142.7214926816769</v>
+        <v>142.2437306026692</v>
       </c>
       <c r="O44">
-        <v>38.53480302405276</v>
+        <v>38.40580726272069</v>
       </c>
       <c r="P44">
-        <v>104.1866896576241</v>
+        <v>103.8379233399485</v>
       </c>
       <c r="Q44">
-        <v>152.9866896576241</v>
+        <v>152.6379233399485</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1651372350439278</v>
+        <v>0.1668610722454204</v>
       </c>
       <c r="T44">
-        <v>1.429629325548682</v>
+        <v>1.45028045103201</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.112600449983493</v>
+        <v>7.92393532323969</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1119044611798896</v>
+        <v>0.1116262260343011</v>
       </c>
       <c r="C45">
-        <v>610.5249845750932</v>
+        <v>605.3018546129938</v>
       </c>
       <c r="D45">
-        <v>877.0206742448274</v>
+        <v>880.7276766006289</v>
       </c>
       <c r="E45">
-        <v>-20.51754212034547</v>
+        <v>-11.58740980244465</v>
       </c>
       <c r="F45">
-        <v>383.9956896697343</v>
+        <v>392.9258219876351</v>
       </c>
       <c r="G45">
         <v>117.5</v>
@@ -4977,28 +4977,28 @@
         <v>162.7875</v>
       </c>
       <c r="M45">
-        <v>20.54376939733078</v>
+        <v>21.02153147633848</v>
       </c>
       <c r="N45">
-        <v>142.2437306026692</v>
+        <v>141.7659685236615</v>
       </c>
       <c r="O45">
-        <v>38.40580726272069</v>
+        <v>38.2768115013886</v>
       </c>
       <c r="P45">
-        <v>103.8379233399485</v>
+        <v>103.4891570222729</v>
       </c>
       <c r="Q45">
-        <v>152.6379233399485</v>
+        <v>152.2891570222729</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1668610722454204</v>
+        <v>0.1686464750612519</v>
       </c>
       <c r="T45">
-        <v>1.45028045103201</v>
+        <v>1.471669116711171</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.92393532323969</v>
+        <v>7.743845884075151</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1116262260343011</v>
+        <v>0.1116107908887126</v>
       </c>
       <c r="C46">
-        <v>605.3018546129938</v>
+        <v>596.5782865944821</v>
       </c>
       <c r="D46">
-        <v>880.7276766006289</v>
+        <v>880.9342409000179</v>
       </c>
       <c r="E46">
-        <v>-11.58740980244465</v>
+        <v>-2.65727748454384</v>
       </c>
       <c r="F46">
-        <v>392.9258219876351</v>
+        <v>401.8559543055359</v>
       </c>
       <c r="G46">
         <v>117.5</v>
@@ -5059,45 +5059,45 @@
         <v>162.7875</v>
       </c>
       <c r="M46">
-        <v>21.02153147633848</v>
+        <v>21.8207783187906</v>
       </c>
       <c r="N46">
-        <v>141.7659685236615</v>
+        <v>140.9667216812094</v>
       </c>
       <c r="O46">
-        <v>38.2768115013886</v>
+        <v>38.06101485392654</v>
       </c>
       <c r="P46">
-        <v>103.4891570222729</v>
+        <v>102.9057068272828</v>
       </c>
       <c r="Q46">
-        <v>152.2891570222729</v>
+        <v>151.7057068272828</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1686464750612519</v>
+        <v>0.170496801615841</v>
       </c>
       <c r="T46">
-        <v>1.471669116711171</v>
+        <v>1.493835552051392</v>
       </c>
       <c r="U46">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V46">
         <v>0.27</v>
       </c>
       <c r="W46">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y46">
-        <v>7.743845884075151</v>
+        <v>7.460205938658852</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1116107908887126</v>
+        <v>0.111338395743124</v>
       </c>
       <c r="C47">
-        <v>596.5782865944821</v>
+        <v>591.3095531876013</v>
       </c>
       <c r="D47">
-        <v>880.9342409000179</v>
+        <v>884.5956398110379</v>
       </c>
       <c r="E47">
-        <v>-2.65727748454384</v>
+        <v>6.272854833356917</v>
       </c>
       <c r="F47">
-        <v>401.8559543055359</v>
+        <v>410.7860866234367</v>
       </c>
       <c r="G47">
         <v>117.5</v>
@@ -5141,28 +5141,28 @@
         <v>162.7875</v>
       </c>
       <c r="M47">
-        <v>21.8207783187906</v>
+        <v>22.30568450365261</v>
       </c>
       <c r="N47">
-        <v>140.9667216812094</v>
+        <v>140.4818154963473</v>
       </c>
       <c r="O47">
-        <v>38.06101485392654</v>
+        <v>37.93009018401379</v>
       </c>
       <c r="P47">
-        <v>102.9057068272828</v>
+        <v>102.5517253123336</v>
       </c>
       <c r="Q47">
-        <v>151.7057068272828</v>
+        <v>151.3517253123335</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.170496801615841</v>
+        <v>0.172415658783563</v>
       </c>
       <c r="T47">
-        <v>1.493835552051392</v>
+        <v>1.516822966478288</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.460205938658852</v>
+        <v>7.298027548688007</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.111338395743124</v>
+        <v>0.1110660005975355</v>
       </c>
       <c r="C48">
-        <v>591.3095531876013</v>
+        <v>586.0713823180387</v>
       </c>
       <c r="D48">
-        <v>884.5956398110379</v>
+        <v>888.2876012593762</v>
       </c>
       <c r="E48">
-        <v>6.272854833356917</v>
+        <v>15.20298715125773</v>
       </c>
       <c r="F48">
-        <v>410.7860866234367</v>
+        <v>419.7162189413375</v>
       </c>
       <c r="G48">
         <v>117.5</v>
@@ -5223,28 +5223,28 @@
         <v>162.7875</v>
       </c>
       <c r="M48">
-        <v>22.30568450365261</v>
+        <v>22.79059068851463</v>
       </c>
       <c r="N48">
-        <v>140.4818154963473</v>
+        <v>139.9969093114854</v>
       </c>
       <c r="O48">
-        <v>37.93009018401379</v>
+        <v>37.79916551410105</v>
       </c>
       <c r="P48">
-        <v>102.5517253123336</v>
+        <v>102.1977437973843</v>
       </c>
       <c r="Q48">
-        <v>151.3517253123335</v>
+        <v>150.9977437973843</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.172415658783563</v>
+        <v>0.1744069256557273</v>
       </c>
       <c r="T48">
-        <v>1.516822966478288</v>
+        <v>1.540677830506199</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.298027548688007</v>
+        <v>7.14275036680103</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1110660005975355</v>
+        <v>0.110793605451947</v>
       </c>
       <c r="C49">
-        <v>586.0713823180387</v>
+        <v>580.864158258373</v>
       </c>
       <c r="D49">
-        <v>888.2876012593762</v>
+        <v>892.0105095176114</v>
       </c>
       <c r="E49">
-        <v>15.20298715125773</v>
+        <v>24.13311946915854</v>
       </c>
       <c r="F49">
-        <v>419.7162189413375</v>
+        <v>428.6463512592383</v>
       </c>
       <c r="G49">
         <v>117.5</v>
@@ -5305,28 +5305,28 @@
         <v>162.7875</v>
       </c>
       <c r="M49">
-        <v>22.79059068851463</v>
+        <v>23.27549687337664</v>
       </c>
       <c r="N49">
-        <v>139.9969093114854</v>
+        <v>139.5120031266233</v>
       </c>
       <c r="O49">
-        <v>37.79916551410105</v>
+        <v>37.6682408441883</v>
       </c>
       <c r="P49">
-        <v>102.1977437973843</v>
+        <v>101.843762282435</v>
       </c>
       <c r="Q49">
-        <v>150.9977437973843</v>
+        <v>150.643762282435</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1744069256557273</v>
+        <v>0.1764747797152826</v>
       </c>
       <c r="T49">
-        <v>1.540677830506199</v>
+        <v>1.565450189304414</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.14275036680103</v>
+        <v>6.993943067492673</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.110793605451947</v>
+        <v>0.1105212103063584</v>
       </c>
       <c r="C50">
-        <v>580.8641582583731</v>
+        <v>575.6882717504072</v>
       </c>
       <c r="D50">
-        <v>892.0105095176114</v>
+        <v>895.7647553275464</v>
       </c>
       <c r="E50">
-        <v>24.13311946915849</v>
+        <v>33.0632517870593</v>
       </c>
       <c r="F50">
-        <v>428.6463512592383</v>
+        <v>437.5764835771391</v>
       </c>
       <c r="G50">
         <v>117.5</v>
@@ -5387,28 +5387,28 @@
         <v>162.7875</v>
       </c>
       <c r="M50">
-        <v>23.27549687337664</v>
+        <v>23.76040305823865</v>
       </c>
       <c r="N50">
-        <v>139.5120031266233</v>
+        <v>139.0270969417613</v>
       </c>
       <c r="O50">
-        <v>37.6682408441883</v>
+        <v>37.53731617427556</v>
       </c>
       <c r="P50">
-        <v>101.843762282435</v>
+        <v>101.4897807674858</v>
       </c>
       <c r="Q50">
-        <v>150.643762282435</v>
+        <v>150.2897807674858</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1764747797152826</v>
+        <v>0.1786237260908989</v>
       </c>
       <c r="T50">
-        <v>1.565450189304414</v>
+        <v>1.591194013153539</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.993943067492674</v>
+        <v>6.851209535503029</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1105212103063584</v>
+        <v>0.1102488151607699</v>
       </c>
       <c r="C51">
-        <v>575.6882717504072</v>
+        <v>570.5441201418778</v>
       </c>
       <c r="D51">
-        <v>895.7647553275464</v>
+        <v>899.5507360369177</v>
       </c>
       <c r="E51">
-        <v>33.0632517870593</v>
+        <v>41.99338410496011</v>
       </c>
       <c r="F51">
-        <v>437.5764835771391</v>
+        <v>446.5066158950399</v>
       </c>
       <c r="G51">
         <v>117.5</v>
@@ -5469,28 +5469,28 @@
         <v>162.7875</v>
       </c>
       <c r="M51">
-        <v>23.76040305823865</v>
+        <v>24.24530924310067</v>
       </c>
       <c r="N51">
-        <v>139.0270969417613</v>
+        <v>138.5421907568993</v>
       </c>
       <c r="O51">
-        <v>37.53731617427556</v>
+        <v>37.40639150436281</v>
       </c>
       <c r="P51">
-        <v>101.4897807674858</v>
+        <v>101.1357992525365</v>
       </c>
       <c r="Q51">
-        <v>150.2897807674858</v>
+        <v>149.9357992525365</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1786237260908989</v>
+        <v>0.1808586303215398</v>
       </c>
       <c r="T51">
-        <v>1.591194013153539</v>
+        <v>1.61796758995663</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.851209535503029</v>
+        <v>6.714185344792966</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1102488151607699</v>
+        <v>0.1099764200151814</v>
       </c>
       <c r="C52">
-        <v>570.5441201418778</v>
+        <v>565.4321075266507</v>
       </c>
       <c r="D52">
-        <v>899.5507360369177</v>
+        <v>903.3688557395915</v>
       </c>
       <c r="E52">
-        <v>41.99338410496011</v>
+        <v>50.92351642286093</v>
       </c>
       <c r="F52">
-        <v>446.5066158950399</v>
+        <v>455.4367482129407</v>
       </c>
       <c r="G52">
         <v>117.5</v>
@@ -5551,28 +5551,28 @@
         <v>162.7875</v>
       </c>
       <c r="M52">
-        <v>24.24530924310067</v>
+        <v>24.73021542796268</v>
       </c>
       <c r="N52">
-        <v>138.5421907568993</v>
+        <v>138.0572845720373</v>
       </c>
       <c r="O52">
-        <v>37.40639150436281</v>
+        <v>37.27546683445006</v>
       </c>
       <c r="P52">
-        <v>101.1357992525365</v>
+        <v>100.7818177375872</v>
       </c>
       <c r="Q52">
-        <v>149.9357992525365</v>
+        <v>149.5818177375872</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1808586303215398</v>
+        <v>0.1831847551330232</v>
       </c>
       <c r="T52">
-        <v>1.61796758995663</v>
+        <v>1.645833965812908</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.714185344792966</v>
+        <v>6.58253465175781</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1099764200151814</v>
+        <v>0.1097040248695928</v>
       </c>
       <c r="C53">
-        <v>565.4321075266507</v>
+        <v>560.3526448885001</v>
       </c>
       <c r="D53">
-        <v>903.3688557395915</v>
+        <v>907.2195254193415</v>
       </c>
       <c r="E53">
-        <v>50.92351642286093</v>
+        <v>59.85364874076174</v>
       </c>
       <c r="F53">
-        <v>455.4367482129407</v>
+        <v>464.3668805308415</v>
       </c>
       <c r="G53">
         <v>117.5</v>
@@ -5633,28 +5633,28 @@
         <v>162.7875</v>
       </c>
       <c r="M53">
-        <v>24.73021542796268</v>
+        <v>25.2151216128247</v>
       </c>
       <c r="N53">
-        <v>138.0572845720373</v>
+        <v>137.5723783871753</v>
       </c>
       <c r="O53">
-        <v>37.27546683445006</v>
+        <v>37.14454216453732</v>
       </c>
       <c r="P53">
-        <v>100.7818177375872</v>
+        <v>100.4278362226379</v>
       </c>
       <c r="Q53">
-        <v>149.5818177375872</v>
+        <v>149.227836222638</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1831847551330232</v>
+        <v>0.1856078018116518</v>
       </c>
       <c r="T53">
-        <v>1.645833965812908</v>
+        <v>1.674861440663197</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.58253465175781</v>
+        <v>6.455947446916314</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1097040248695928</v>
+        <v>0.1094316297240043</v>
       </c>
       <c r="C54">
-        <v>560.3526448885001</v>
+        <v>555.3061502485784</v>
       </c>
       <c r="D54">
-        <v>907.2195254193415</v>
+        <v>911.1031630973208</v>
       </c>
       <c r="E54">
-        <v>59.85364874076174</v>
+        <v>68.78378105866256</v>
       </c>
       <c r="F54">
-        <v>464.3668805308415</v>
+        <v>473.2970128487423</v>
       </c>
       <c r="G54">
         <v>117.5</v>
@@ -5715,28 +5715,28 @@
         <v>162.7875</v>
       </c>
       <c r="M54">
-        <v>25.2151216128247</v>
+        <v>25.70002779768671</v>
       </c>
       <c r="N54">
-        <v>137.5723783871753</v>
+        <v>137.0874722023133</v>
       </c>
       <c r="O54">
-        <v>37.14454216453732</v>
+        <v>37.01361749462458</v>
       </c>
       <c r="P54">
-        <v>100.4278362226379</v>
+        <v>100.0738547076887</v>
       </c>
       <c r="Q54">
-        <v>149.227836222638</v>
+        <v>148.8738547076887</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1856078018116518</v>
+        <v>0.1881339568595836</v>
       </c>
       <c r="T54">
-        <v>1.674861440663197</v>
+        <v>1.705124127209244</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.455947446916314</v>
+        <v>6.334137117729214</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1094316297240043</v>
+        <v>0.1091592345784158</v>
       </c>
       <c r="C55">
-        <v>555.3061502485784</v>
+        <v>550.2930488166951</v>
       </c>
       <c r="D55">
-        <v>911.1031630973208</v>
+        <v>915.0201939833381</v>
       </c>
       <c r="E55">
-        <v>68.78378105866256</v>
+        <v>77.71391337656331</v>
       </c>
       <c r="F55">
-        <v>473.2970128487423</v>
+        <v>482.2271451666431</v>
       </c>
       <c r="G55">
         <v>117.5</v>
@@ -5797,28 +5797,28 @@
         <v>162.7875</v>
       </c>
       <c r="M55">
-        <v>25.70002779768671</v>
+        <v>26.18493398254872</v>
       </c>
       <c r="N55">
-        <v>137.0874722023133</v>
+        <v>136.6025660174512</v>
       </c>
       <c r="O55">
-        <v>37.01361749462458</v>
+        <v>36.88269282471184</v>
       </c>
       <c r="P55">
-        <v>100.0738547076887</v>
+        <v>99.7198731927394</v>
       </c>
       <c r="Q55">
-        <v>148.8738547076887</v>
+        <v>148.5198731927394</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1881339568595836</v>
+        <v>0.1907699447356865</v>
       </c>
       <c r="T55">
-        <v>1.705124127209244</v>
+        <v>1.736702582735553</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.334137117729214</v>
+        <v>6.21683828221571</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1091592345784158</v>
+        <v>0.1092883394328272</v>
       </c>
       <c r="C56">
-        <v>550.2930488166951</v>
+        <v>539.5022039650731</v>
       </c>
       <c r="D56">
-        <v>915.0201939833381</v>
+        <v>913.1594814496171</v>
       </c>
       <c r="E56">
-        <v>77.71391337656331</v>
+        <v>86.64404569446413</v>
       </c>
       <c r="F56">
-        <v>482.2271451666431</v>
+        <v>491.1572774845439</v>
       </c>
       <c r="G56">
         <v>117.5</v>
@@ -5879,45 +5879,45 @@
         <v>162.7875</v>
       </c>
       <c r="M56">
-        <v>26.18493398254872</v>
+        <v>27.16099744489528</v>
       </c>
       <c r="N56">
-        <v>136.6025660174512</v>
+        <v>135.6265025551047</v>
       </c>
       <c r="O56">
-        <v>36.88269282471184</v>
+        <v>36.61915568987826</v>
       </c>
       <c r="P56">
-        <v>99.7198731927394</v>
+        <v>99.00734686522642</v>
       </c>
       <c r="Q56">
-        <v>148.5198731927394</v>
+        <v>147.8073468652264</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1907699447356865</v>
+        <v>0.193523087628505</v>
       </c>
       <c r="T56">
-        <v>1.736702582735553</v>
+        <v>1.769684525174143</v>
       </c>
       <c r="U56">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V56">
         <v>0.27</v>
       </c>
       <c r="W56">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>6.21683828221571</v>
+        <v>5.993428640839356</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1092883394328272</v>
+        <v>0.1090232442872387</v>
       </c>
       <c r="C57">
-        <v>539.5022039650731</v>
+        <v>534.4009505414701</v>
       </c>
       <c r="D57">
-        <v>913.1594814496171</v>
+        <v>916.9883603439148</v>
       </c>
       <c r="E57">
-        <v>86.64404569446413</v>
+        <v>95.57417801236494</v>
       </c>
       <c r="F57">
-        <v>491.1572774845439</v>
+        <v>500.0874098024447</v>
       </c>
       <c r="G57">
         <v>117.5</v>
@@ -5961,28 +5961,28 @@
         <v>162.7875</v>
       </c>
       <c r="M57">
-        <v>27.16099744489528</v>
+        <v>27.65483376207519</v>
       </c>
       <c r="N57">
-        <v>135.6265025551047</v>
+        <v>135.1326662379248</v>
       </c>
       <c r="O57">
-        <v>36.61915568987826</v>
+        <v>36.4858198842397</v>
       </c>
       <c r="P57">
-        <v>99.00734686522642</v>
+        <v>98.64684635368508</v>
       </c>
       <c r="Q57">
-        <v>147.8073468652264</v>
+        <v>147.4468463536851</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.193523087628505</v>
+        <v>0.196401373380088</v>
       </c>
       <c r="T57">
-        <v>1.769684525174143</v>
+        <v>1.804165646814487</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.993428640839356</v>
+        <v>5.886403129395798</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1090232442872387</v>
+        <v>0.1087581491416502</v>
       </c>
       <c r="C58">
-        <v>534.4009505414701</v>
+        <v>529.3319413061656</v>
       </c>
       <c r="D58">
-        <v>916.9883603439148</v>
+        <v>920.849483426511</v>
       </c>
       <c r="E58">
-        <v>95.57417801236494</v>
+        <v>104.5043103302658</v>
       </c>
       <c r="F58">
-        <v>500.0874098024447</v>
+        <v>509.0175421203455</v>
       </c>
       <c r="G58">
         <v>117.5</v>
@@ -6043,28 +6043,28 @@
         <v>162.7875</v>
       </c>
       <c r="M58">
-        <v>27.65483376207519</v>
+        <v>28.14867007925511</v>
       </c>
       <c r="N58">
-        <v>135.1326662379248</v>
+        <v>134.6388299207449</v>
       </c>
       <c r="O58">
-        <v>36.4858198842397</v>
+        <v>36.35248407860112</v>
       </c>
       <c r="P58">
-        <v>98.64684635368508</v>
+        <v>98.28634584214373</v>
       </c>
       <c r="Q58">
-        <v>147.4468463536851</v>
+        <v>147.0863458421437</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.196401373380088</v>
+        <v>0.1994135328875586</v>
       </c>
       <c r="T58">
-        <v>1.804165646814487</v>
+        <v>1.840250541554382</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.886403129395798</v>
+        <v>5.78313289905552</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1087581491416502</v>
+        <v>0.1084930539960617</v>
       </c>
       <c r="C59">
-        <v>529.3319413061656</v>
+        <v>524.2955852890556</v>
       </c>
       <c r="D59">
-        <v>920.849483426511</v>
+        <v>924.7432597273017</v>
       </c>
       <c r="E59">
-        <v>104.5043103302658</v>
+        <v>113.4344426481665</v>
       </c>
       <c r="F59">
-        <v>509.0175421203455</v>
+        <v>517.9476744382463</v>
       </c>
       <c r="G59">
         <v>117.5</v>
@@ -6125,28 +6125,28 @@
         <v>162.7875</v>
       </c>
       <c r="M59">
-        <v>28.14867007925511</v>
+        <v>28.64250639643502</v>
       </c>
       <c r="N59">
-        <v>134.6388299207449</v>
+        <v>134.144993603565</v>
       </c>
       <c r="O59">
-        <v>36.35248407860112</v>
+        <v>36.21914827296254</v>
       </c>
       <c r="P59">
-        <v>98.28634584214373</v>
+        <v>97.92584533060241</v>
       </c>
       <c r="Q59">
-        <v>147.0863458421437</v>
+        <v>146.7258453306024</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1994135328875586</v>
+        <v>0.2025691285620516</v>
       </c>
       <c r="T59">
-        <v>1.840250541554382</v>
+        <v>1.878053764615224</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.78313289905552</v>
+        <v>5.683423711140771</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1084930539960617</v>
+        <v>0.1082279588504731</v>
       </c>
       <c r="C60">
-        <v>524.2955852890558</v>
+        <v>519.2922984676829</v>
       </c>
       <c r="D60">
-        <v>924.7432597273021</v>
+        <v>928.6701052238301</v>
       </c>
       <c r="E60">
-        <v>113.4344426481665</v>
+        <v>122.3645749660673</v>
       </c>
       <c r="F60">
-        <v>517.9476744382463</v>
+        <v>526.877806756147</v>
       </c>
       <c r="G60">
         <v>117.5</v>
@@ -6207,28 +6207,28 @@
         <v>162.7875</v>
       </c>
       <c r="M60">
-        <v>28.64250639643502</v>
+        <v>29.13634271361493</v>
       </c>
       <c r="N60">
-        <v>134.144993603565</v>
+        <v>133.651157286385</v>
       </c>
       <c r="O60">
-        <v>36.21914827296254</v>
+        <v>36.08581246732396</v>
       </c>
       <c r="P60">
-        <v>97.92584533060241</v>
+        <v>97.56534481906107</v>
       </c>
       <c r="Q60">
-        <v>146.7258453306024</v>
+        <v>146.3653448190611</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2025691285620515</v>
+        <v>0.2058786557328613</v>
       </c>
       <c r="T60">
-        <v>1.878053764615224</v>
+        <v>1.91770104733757</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.683423711140771</v>
+        <v>5.587094495697706</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1082279588504731</v>
+        <v>0.1079628637048846</v>
       </c>
       <c r="C61">
-        <v>519.2922984676829</v>
+        <v>514.322503915378</v>
       </c>
       <c r="D61">
-        <v>928.6701052238301</v>
+        <v>932.6304429894257</v>
       </c>
       <c r="E61">
-        <v>122.3645749660673</v>
+        <v>131.294707283968</v>
       </c>
       <c r="F61">
-        <v>526.877806756147</v>
+        <v>535.8079390740478</v>
       </c>
       <c r="G61">
         <v>117.5</v>
@@ -6289,28 +6289,28 @@
         <v>162.7875</v>
       </c>
       <c r="M61">
-        <v>29.13634271361493</v>
+        <v>29.63017903079485</v>
       </c>
       <c r="N61">
-        <v>133.651157286385</v>
+        <v>133.1573209692051</v>
       </c>
       <c r="O61">
-        <v>36.08581246732396</v>
+        <v>35.95247666168539</v>
       </c>
       <c r="P61">
-        <v>97.56534481906107</v>
+        <v>97.20484430751975</v>
       </c>
       <c r="Q61">
-        <v>146.3653448190611</v>
+        <v>146.0048443075198</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2058786557328613</v>
+        <v>0.2093536592622115</v>
       </c>
       <c r="T61">
-        <v>1.91770104733757</v>
+        <v>1.959330694196034</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.587094495697706</v>
+        <v>5.493976254102745</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1079628637048846</v>
+        <v>0.1076977685592961</v>
       </c>
       <c r="C62">
-        <v>514.322503915378</v>
+        <v>509.3866319532073</v>
       </c>
       <c r="D62">
-        <v>932.6304429894257</v>
+        <v>936.6247033451559</v>
       </c>
       <c r="E62">
-        <v>131.294707283968</v>
+        <v>140.2248396018689</v>
       </c>
       <c r="F62">
-        <v>535.8079390740478</v>
+        <v>544.7380713919487</v>
       </c>
       <c r="G62">
         <v>117.5</v>
@@ -6371,28 +6371,28 @@
         <v>162.7875</v>
       </c>
       <c r="M62">
-        <v>29.63017903079485</v>
+        <v>30.12401534797476</v>
       </c>
       <c r="N62">
-        <v>133.1573209692051</v>
+        <v>132.6634846520252</v>
       </c>
       <c r="O62">
-        <v>35.95247666168539</v>
+        <v>35.81914085604681</v>
       </c>
       <c r="P62">
-        <v>97.20484430751975</v>
+        <v>96.8443437959784</v>
       </c>
       <c r="Q62">
-        <v>146.0048443075198</v>
+        <v>145.6443437959784</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2093536592622115</v>
+        <v>0.2130068681007592</v>
       </c>
       <c r="T62">
-        <v>1.959330694196034</v>
+        <v>2.003095194739548</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.493976254102745</v>
+        <v>5.403911069609257</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1076977685592961</v>
+        <v>0.1074326734137075</v>
       </c>
       <c r="C63">
-        <v>509.3866319532073</v>
+        <v>504.4851203058467</v>
       </c>
       <c r="D63">
-        <v>936.6247033451559</v>
+        <v>940.6533240156962</v>
       </c>
       <c r="E63">
-        <v>140.2248396018689</v>
+        <v>149.1549719197697</v>
       </c>
       <c r="F63">
-        <v>544.7380713919487</v>
+        <v>553.6682037098494</v>
       </c>
       <c r="G63">
         <v>117.5</v>
@@ -6453,28 +6453,28 @@
         <v>162.7875</v>
       </c>
       <c r="M63">
-        <v>30.12401534797476</v>
+        <v>30.61785166515467</v>
       </c>
       <c r="N63">
-        <v>132.6634846520252</v>
+        <v>132.1696483348453</v>
       </c>
       <c r="O63">
-        <v>35.81914085604681</v>
+        <v>35.68580505040823</v>
       </c>
       <c r="P63">
-        <v>96.8443437959784</v>
+        <v>96.48384328443707</v>
       </c>
       <c r="Q63">
-        <v>145.6443437959784</v>
+        <v>145.2838432844371</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2130068681007592</v>
+        <v>0.216852351088704</v>
       </c>
       <c r="T63">
-        <v>2.003095194739548</v>
+        <v>2.04916309004851</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.403911069609257</v>
+        <v>5.316751213647818</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1074326734137075</v>
+        <v>0.107167578268119</v>
       </c>
       <c r="C64">
-        <v>504.4851203058467</v>
+        <v>499.6184142614873</v>
       </c>
       <c r="D64">
-        <v>940.6533240156962</v>
+        <v>944.7167502892376</v>
       </c>
       <c r="E64">
-        <v>149.1549719197697</v>
+        <v>158.0851042376705</v>
       </c>
       <c r="F64">
-        <v>553.6682037098494</v>
+        <v>562.5983360277503</v>
       </c>
       <c r="G64">
         <v>117.5</v>
@@ -6535,28 +6535,28 @@
         <v>162.7875</v>
       </c>
       <c r="M64">
-        <v>30.61785166515467</v>
+        <v>31.11168798233459</v>
       </c>
       <c r="N64">
-        <v>132.1696483348453</v>
+        <v>131.6758120176654</v>
       </c>
       <c r="O64">
-        <v>35.68580505040823</v>
+        <v>35.55246924476965</v>
       </c>
       <c r="P64">
-        <v>96.48384328443707</v>
+        <v>96.12334277289573</v>
       </c>
       <c r="Q64">
-        <v>145.2838432844371</v>
+        <v>144.9233427728957</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.216852351088704</v>
+        <v>0.2209056980219432</v>
       </c>
       <c r="T64">
-        <v>2.04916309004851</v>
+        <v>2.097721141860658</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.316751213647818</v>
+        <v>5.232358337240709</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.107167578268119</v>
+        <v>0.1069024831225305</v>
       </c>
       <c r="C65">
-        <v>499.6184142614873</v>
+        <v>494.7869668359109</v>
       </c>
       <c r="D65">
-        <v>944.7167502892376</v>
+        <v>948.8154351815621</v>
       </c>
       <c r="E65">
-        <v>158.0851042376705</v>
+        <v>167.0152365555713</v>
       </c>
       <c r="F65">
-        <v>562.5983360277503</v>
+        <v>571.528468345651</v>
       </c>
       <c r="G65">
         <v>117.5</v>
@@ -6617,28 +6617,28 @@
         <v>162.7875</v>
       </c>
       <c r="M65">
-        <v>31.11168798233459</v>
+        <v>31.6055242995145</v>
       </c>
       <c r="N65">
-        <v>131.6758120176654</v>
+        <v>131.1819757004855</v>
       </c>
       <c r="O65">
-        <v>35.55246924476965</v>
+        <v>35.41913343913107</v>
       </c>
       <c r="P65">
-        <v>96.12334277289573</v>
+        <v>95.76284226135438</v>
       </c>
       <c r="Q65">
-        <v>144.9233427728957</v>
+        <v>144.5628422613544</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2209056980219432</v>
+        <v>0.225184230895918</v>
       </c>
       <c r="T65">
-        <v>2.097721141860658</v>
+        <v>2.148976863217926</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.232358337240709</v>
+        <v>5.150602738221322</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1069024831225305</v>
+        <v>0.1066373879769419</v>
       </c>
       <c r="C66">
-        <v>494.7869668359109</v>
+        <v>489.9912389408536</v>
       </c>
       <c r="D66">
-        <v>948.8154351815621</v>
+        <v>952.9498396044055</v>
       </c>
       <c r="E66">
-        <v>167.0152365555713</v>
+        <v>175.9453688734721</v>
       </c>
       <c r="F66">
-        <v>571.528468345651</v>
+        <v>580.4586006635519</v>
       </c>
       <c r="G66">
         <v>117.5</v>
@@ -6699,28 +6699,28 @@
         <v>162.7875</v>
       </c>
       <c r="M66">
-        <v>31.6055242995145</v>
+        <v>32.09936061669442</v>
       </c>
       <c r="N66">
-        <v>131.1819757004855</v>
+        <v>130.6881393833056</v>
       </c>
       <c r="O66">
-        <v>35.41913343913107</v>
+        <v>35.2857976334925</v>
       </c>
       <c r="P66">
-        <v>95.76284226135438</v>
+        <v>95.40234174981305</v>
       </c>
       <c r="Q66">
-        <v>144.5628422613544</v>
+        <v>144.2023417498131</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.225184230895918</v>
+        <v>0.2297072513626913</v>
       </c>
       <c r="T66">
-        <v>2.148976863217926</v>
+        <v>2.203161482938467</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.150602738221322</v>
+        <v>5.071362696094841</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1066373879769419</v>
+        <v>0.1063722928313534</v>
       </c>
       <c r="C67">
-        <v>489.9912389408536</v>
+        <v>485.2316995567858</v>
       </c>
       <c r="D67">
-        <v>952.9498396044055</v>
+        <v>957.1204325382384</v>
       </c>
       <c r="E67">
-        <v>175.9453688734721</v>
+        <v>184.8755011913729</v>
       </c>
       <c r="F67">
-        <v>580.4586006635519</v>
+        <v>589.3887329814527</v>
       </c>
       <c r="G67">
         <v>117.5</v>
@@ -6781,28 +6781,28 @@
         <v>162.7875</v>
       </c>
       <c r="M67">
-        <v>32.09936061669442</v>
+        <v>32.59319693387433</v>
       </c>
       <c r="N67">
-        <v>130.6881393833056</v>
+        <v>130.1943030661256</v>
       </c>
       <c r="O67">
-        <v>35.2857976334925</v>
+        <v>35.15246182785392</v>
       </c>
       <c r="P67">
-        <v>95.40234174981305</v>
+        <v>95.0418412382717</v>
       </c>
       <c r="Q67">
-        <v>144.2023417498131</v>
+        <v>143.8418412382717</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2297072513626913</v>
+        <v>0.2344963318569218</v>
       </c>
       <c r="T67">
-        <v>2.203161482938467</v>
+        <v>2.260533433230803</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.071362696094841</v>
+        <v>4.994523867366132</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1063722928313534</v>
+        <v>0.1061071976857649</v>
       </c>
       <c r="C68">
-        <v>485.2316995567858</v>
+        <v>480.508825910255</v>
       </c>
       <c r="D68">
-        <v>957.1204325382384</v>
+        <v>961.3276912096086</v>
       </c>
       <c r="E68">
-        <v>184.8755011913729</v>
+        <v>193.8056335092737</v>
       </c>
       <c r="F68">
-        <v>589.3887329814527</v>
+        <v>598.3188652993534</v>
       </c>
       <c r="G68">
         <v>117.5</v>
@@ -6863,28 +6863,28 @@
         <v>162.7875</v>
       </c>
       <c r="M68">
-        <v>32.59319693387433</v>
+        <v>33.08703325105424</v>
       </c>
       <c r="N68">
-        <v>130.1943030661256</v>
+        <v>129.7004667489457</v>
       </c>
       <c r="O68">
-        <v>35.15246182785392</v>
+        <v>35.01912602221535</v>
       </c>
       <c r="P68">
-        <v>95.0418412382717</v>
+        <v>94.68134072673038</v>
       </c>
       <c r="Q68">
-        <v>143.8418412382717</v>
+        <v>143.4813407267304</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2344963318569218</v>
+        <v>0.239575659653833</v>
       </c>
       <c r="T68">
-        <v>2.260533433230803</v>
+        <v>2.321382471419646</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.994523867366132</v>
+        <v>4.919978735017384</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1061071976857649</v>
+        <v>0.1058421025401763</v>
       </c>
       <c r="C69">
-        <v>480.508825910255</v>
+        <v>475.8231036559258</v>
       </c>
       <c r="D69">
-        <v>961.3276912096086</v>
+        <v>965.5721012731801</v>
       </c>
       <c r="E69">
-        <v>193.8056335092737</v>
+        <v>202.7357658271745</v>
       </c>
       <c r="F69">
-        <v>598.3188652993534</v>
+        <v>607.2489976172543</v>
       </c>
       <c r="G69">
         <v>117.5</v>
@@ -6945,28 +6945,28 @@
         <v>162.7875</v>
       </c>
       <c r="M69">
-        <v>33.08703325105424</v>
+        <v>33.58086956823416</v>
       </c>
       <c r="N69">
-        <v>129.7004667489457</v>
+        <v>129.2066304317658</v>
       </c>
       <c r="O69">
-        <v>35.01912602221535</v>
+        <v>34.88579021657677</v>
       </c>
       <c r="P69">
-        <v>94.68134072673038</v>
+        <v>94.32084021518904</v>
       </c>
       <c r="Q69">
-        <v>143.4813407267304</v>
+        <v>143.120840215189</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.239575659653833</v>
+        <v>0.2449724454380511</v>
       </c>
       <c r="T69">
-        <v>2.321382471419646</v>
+        <v>2.38603457449529</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.919978735017384</v>
+        <v>4.847626106561245</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1058421025401763</v>
+        <v>0.1055770073945878</v>
       </c>
       <c r="C70">
-        <v>475.8231036559258</v>
+        <v>471.1750270634579</v>
       </c>
       <c r="D70">
-        <v>965.5721012731801</v>
+        <v>969.854156998613</v>
       </c>
       <c r="E70">
-        <v>202.7357658271745</v>
+        <v>211.6658981450753</v>
       </c>
       <c r="F70">
-        <v>607.2489976172543</v>
+        <v>616.1791299351551</v>
       </c>
       <c r="G70">
         <v>117.5</v>
@@ -7027,28 +7027,28 @@
         <v>162.7875</v>
       </c>
       <c r="M70">
-        <v>33.58086956823416</v>
+        <v>34.07470588541408</v>
       </c>
       <c r="N70">
-        <v>129.2066304317658</v>
+        <v>128.7127941145859</v>
       </c>
       <c r="O70">
-        <v>34.88579021657677</v>
+        <v>34.7524544109382</v>
       </c>
       <c r="P70">
-        <v>94.32084021518904</v>
+        <v>93.9603397036477</v>
       </c>
       <c r="Q70">
-        <v>143.120840215189</v>
+        <v>142.7603397036477</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2449724454380511</v>
+        <v>0.2507174109502833</v>
       </c>
       <c r="T70">
-        <v>2.38603457449529</v>
+        <v>2.45485778099517</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.847626106561245</v>
+        <v>4.777370655741517</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1055770073945878</v>
+        <v>0.1053119122489993</v>
       </c>
       <c r="C71">
-        <v>471.1750270634579</v>
+        <v>466.565099209387</v>
       </c>
       <c r="D71">
-        <v>969.854156998613</v>
+        <v>974.174361462443</v>
       </c>
       <c r="E71">
-        <v>211.6658981450753</v>
+        <v>220.5960304629762</v>
       </c>
       <c r="F71">
-        <v>616.1791299351551</v>
+        <v>625.1092622530559</v>
       </c>
       <c r="G71">
         <v>117.5</v>
@@ -7109,28 +7109,28 @@
         <v>162.7875</v>
       </c>
       <c r="M71">
-        <v>34.07470588541408</v>
+        <v>34.568542202594</v>
       </c>
       <c r="N71">
-        <v>128.7127941145859</v>
+        <v>128.218957797406</v>
       </c>
       <c r="O71">
-        <v>34.7524544109382</v>
+        <v>34.61911860529962</v>
       </c>
       <c r="P71">
-        <v>93.9603397036477</v>
+        <v>93.59983919210636</v>
       </c>
       <c r="Q71">
-        <v>142.7603397036477</v>
+        <v>142.3998391921064</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2507174109502833</v>
+        <v>0.256845374163331</v>
       </c>
       <c r="T71">
-        <v>2.45485778099517</v>
+        <v>2.528269201261709</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.777370655741517</v>
+        <v>4.709122503516637</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1053119122489993</v>
+        <v>0.1050468171034108</v>
       </c>
       <c r="C72">
-        <v>466.565099209387</v>
+        <v>461.9938321741519</v>
       </c>
       <c r="D72">
-        <v>974.174361462443</v>
+        <v>978.5332267451084</v>
       </c>
       <c r="E72">
-        <v>220.5960304629762</v>
+        <v>229.5261627808769</v>
       </c>
       <c r="F72">
-        <v>625.1092622530559</v>
+        <v>634.0393945709567</v>
       </c>
       <c r="G72">
         <v>117.5</v>
@@ -7191,28 +7191,28 @@
         <v>162.7875</v>
       </c>
       <c r="M72">
-        <v>34.568542202594</v>
+        <v>35.06237851977391</v>
       </c>
       <c r="N72">
-        <v>128.218957797406</v>
+        <v>127.7251214802261</v>
       </c>
       <c r="O72">
-        <v>34.61911860529962</v>
+        <v>34.48578279966104</v>
       </c>
       <c r="P72">
-        <v>93.59983919210636</v>
+        <v>93.23933868056501</v>
       </c>
       <c r="Q72">
-        <v>142.3998391921064</v>
+        <v>142.039338680565</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.256845374163331</v>
+        <v>0.2633959555290027</v>
       </c>
       <c r="T72">
-        <v>2.528269201261709</v>
+        <v>2.606743478098354</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.709122503516637</v>
+        <v>4.642796834453023</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1050468171034108</v>
+        <v>0.1047817219578222</v>
       </c>
       <c r="C73">
-        <v>461.993832174152</v>
+        <v>457.4617472444349</v>
       </c>
       <c r="D73">
-        <v>978.5332267451084</v>
+        <v>982.9312741332925</v>
       </c>
       <c r="E73">
-        <v>229.5261627808768</v>
+        <v>238.4562950987777</v>
       </c>
       <c r="F73">
-        <v>634.0393945709566</v>
+        <v>642.9695268888574</v>
       </c>
       <c r="G73">
         <v>117.5</v>
@@ -7273,28 +7273,28 @@
         <v>162.7875</v>
       </c>
       <c r="M73">
-        <v>35.0623785197739</v>
+        <v>35.55621483695382</v>
       </c>
       <c r="N73">
-        <v>127.7251214802261</v>
+        <v>127.2312851630462</v>
       </c>
       <c r="O73">
-        <v>34.48578279966104</v>
+        <v>34.35244699402246</v>
       </c>
       <c r="P73">
-        <v>93.23933868056503</v>
+        <v>92.87883816902368</v>
       </c>
       <c r="Q73">
-        <v>142.039338680565</v>
+        <v>141.6788381690237</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2633959555290026</v>
+        <v>0.2704144355636509</v>
       </c>
       <c r="T73">
-        <v>2.606743478098354</v>
+        <v>2.69082306042333</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.642796834453024</v>
+        <v>4.578313545085621</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1047817219578222</v>
+        <v>0.1045166268122337</v>
       </c>
       <c r="C74">
-        <v>457.4617472444349</v>
+        <v>452.9693751209876</v>
       </c>
       <c r="D74">
-        <v>982.9312741332925</v>
+        <v>987.3690343277459</v>
       </c>
       <c r="E74">
-        <v>238.4562950987777</v>
+        <v>247.3864274166784</v>
       </c>
       <c r="F74">
-        <v>642.9695268888574</v>
+        <v>651.8996592067582</v>
       </c>
       <c r="G74">
         <v>117.5</v>
@@ -7355,28 +7355,28 @@
         <v>162.7875</v>
       </c>
       <c r="M74">
-        <v>35.55621483695382</v>
+        <v>36.05005115413373</v>
       </c>
       <c r="N74">
-        <v>127.2312851630462</v>
+        <v>126.7374488458662</v>
       </c>
       <c r="O74">
-        <v>34.35244699402246</v>
+        <v>34.21911118838388</v>
       </c>
       <c r="P74">
-        <v>92.87883816902368</v>
+        <v>92.51833765748233</v>
       </c>
       <c r="Q74">
-        <v>141.6788381690237</v>
+        <v>141.3183376574823</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2704144355636509</v>
+        <v>0.2779528030082729</v>
       </c>
       <c r="T74">
-        <v>2.69082306042333</v>
+        <v>2.781130759957564</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.578313545085621</v>
+        <v>4.515596921180338</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1045166268122337</v>
+        <v>0.1056020316666452</v>
       </c>
       <c r="C75">
-        <v>452.9693751209876</v>
+        <v>426.1185281870875</v>
       </c>
       <c r="D75">
-        <v>987.3690343277459</v>
+        <v>969.4483197117465</v>
       </c>
       <c r="E75">
-        <v>247.3864274166784</v>
+        <v>256.3165597345793</v>
       </c>
       <c r="F75">
-        <v>651.8996592067582</v>
+        <v>660.8297915246591</v>
       </c>
       <c r="G75">
         <v>117.5</v>
@@ -7437,45 +7437,45 @@
         <v>162.7875</v>
       </c>
       <c r="M75">
-        <v>36.05005115413373</v>
+        <v>38.19596195012529</v>
       </c>
       <c r="N75">
-        <v>126.7374488458662</v>
+        <v>124.5915380498747</v>
       </c>
       <c r="O75">
-        <v>34.21911118838388</v>
+        <v>33.63971527346617</v>
       </c>
       <c r="P75">
-        <v>92.51833765748233</v>
+        <v>90.95182277640851</v>
       </c>
       <c r="Q75">
-        <v>141.3183376574823</v>
+        <v>139.7518227764085</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2779528030082729</v>
+        <v>0.2860710448717122</v>
       </c>
       <c r="T75">
-        <v>2.781130759957564</v>
+        <v>2.878385205609816</v>
       </c>
       <c r="U75">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V75">
         <v>0.27</v>
       </c>
       <c r="W75">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>4.515596921180338</v>
+        <v>4.261903397342398</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1056020316666452</v>
+        <v>0.1053551865210566</v>
       </c>
       <c r="C76">
-        <v>426.1185281870875</v>
+        <v>421.206578425549</v>
       </c>
       <c r="D76">
-        <v>969.4483197117465</v>
+        <v>973.4665022681088</v>
       </c>
       <c r="E76">
-        <v>256.3165597345793</v>
+        <v>265.2466920524801</v>
       </c>
       <c r="F76">
-        <v>660.8297915246591</v>
+        <v>669.7599238425598</v>
       </c>
       <c r="G76">
         <v>117.5</v>
@@ -7519,28 +7519,28 @@
         <v>162.7875</v>
       </c>
       <c r="M76">
-        <v>38.19596195012529</v>
+        <v>38.71212359809996</v>
       </c>
       <c r="N76">
-        <v>124.5915380498747</v>
+        <v>124.0753764019</v>
       </c>
       <c r="O76">
-        <v>33.63971527346617</v>
+        <v>33.500351628513</v>
       </c>
       <c r="P76">
-        <v>90.95182277640851</v>
+        <v>90.575024773387</v>
       </c>
       <c r="Q76">
-        <v>139.7518227764085</v>
+        <v>139.375024773387</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2860710448717122</v>
+        <v>0.2948387460842265</v>
       </c>
       <c r="T76">
-        <v>2.878385205609816</v>
+        <v>2.983420006914248</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.261903397342398</v>
+        <v>4.205078018711166</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1053551865210566</v>
+        <v>0.1051083413754681</v>
       </c>
       <c r="C77">
-        <v>421.206578425549</v>
+        <v>416.3280765344149</v>
       </c>
       <c r="D77">
-        <v>973.4665022681088</v>
+        <v>977.5181326948754</v>
       </c>
       <c r="E77">
-        <v>265.2466920524801</v>
+        <v>274.1768243703808</v>
       </c>
       <c r="F77">
-        <v>669.7599238425598</v>
+        <v>678.6900561604606</v>
       </c>
       <c r="G77">
         <v>117.5</v>
@@ -7601,28 +7601,28 @@
         <v>162.7875</v>
       </c>
       <c r="M77">
-        <v>38.71212359809996</v>
+        <v>39.22828524607463</v>
       </c>
       <c r="N77">
-        <v>124.0753764019</v>
+        <v>123.5592147539253</v>
       </c>
       <c r="O77">
-        <v>33.500351628513</v>
+        <v>33.36098798355984</v>
       </c>
       <c r="P77">
-        <v>90.575024773387</v>
+        <v>90.19822677036549</v>
       </c>
       <c r="Q77">
-        <v>139.375024773387</v>
+        <v>138.9982267703655</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2948387460842265</v>
+        <v>0.3043370890644505</v>
       </c>
       <c r="T77">
-        <v>2.983420006914248</v>
+        <v>3.097207708327383</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.205078018711166</v>
+        <v>4.149748044780756</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1051083413754681</v>
+        <v>0.1048614962298796</v>
       </c>
       <c r="C78">
-        <v>416.3280765344149</v>
+        <v>411.483441895769</v>
       </c>
       <c r="D78">
-        <v>977.5181326948754</v>
+        <v>981.6036303741305</v>
       </c>
       <c r="E78">
-        <v>274.1768243703808</v>
+        <v>283.1069566882817</v>
       </c>
       <c r="F78">
-        <v>678.6900561604606</v>
+        <v>687.6201884783615</v>
       </c>
       <c r="G78">
         <v>117.5</v>
@@ -7683,28 +7683,28 @@
         <v>162.7875</v>
       </c>
       <c r="M78">
-        <v>39.22828524607463</v>
+        <v>39.7444468940493</v>
       </c>
       <c r="N78">
-        <v>123.5592147539253</v>
+        <v>123.0430531059507</v>
       </c>
       <c r="O78">
-        <v>33.36098798355984</v>
+        <v>33.22162433860668</v>
       </c>
       <c r="P78">
-        <v>90.19822677036549</v>
+        <v>89.82142876734397</v>
       </c>
       <c r="Q78">
-        <v>138.9982267703655</v>
+        <v>138.621428767344</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3043370890644505</v>
+        <v>0.3146613749125199</v>
       </c>
       <c r="T78">
-        <v>3.097207708327383</v>
+        <v>3.220889992472095</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.149748044780756</v>
+        <v>4.095855213030356</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1048614962298796</v>
+        <v>0.104614651084291</v>
       </c>
       <c r="C79">
-        <v>411.483441895769</v>
+        <v>406.6731009322823</v>
       </c>
       <c r="D79">
-        <v>981.6036303741305</v>
+        <v>985.7234217285444</v>
       </c>
       <c r="E79">
-        <v>283.1069566882817</v>
+        <v>292.0370890061824</v>
       </c>
       <c r="F79">
-        <v>687.6201884783615</v>
+        <v>696.5503207962622</v>
       </c>
       <c r="G79">
         <v>117.5</v>
@@ -7765,28 +7765,28 @@
         <v>162.7875</v>
       </c>
       <c r="M79">
-        <v>39.7444468940493</v>
+        <v>40.26060854202396</v>
       </c>
       <c r="N79">
-        <v>123.0430531059507</v>
+        <v>122.526891457976</v>
       </c>
       <c r="O79">
-        <v>33.22162433860668</v>
+        <v>33.08226069365352</v>
       </c>
       <c r="P79">
-        <v>89.82142876734397</v>
+        <v>89.44463076432248</v>
       </c>
       <c r="Q79">
-        <v>138.621428767344</v>
+        <v>138.2446307643225</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3146613749125199</v>
+        <v>0.3259242322013229</v>
       </c>
       <c r="T79">
-        <v>3.220889992472095</v>
+        <v>3.355816120629962</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.095855213030356</v>
+        <v>4.043344248760737</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.104614651084291</v>
+        <v>0.1063862559387025</v>
       </c>
       <c r="C80">
-        <v>406.6731009322823</v>
+        <v>368.9193951490035</v>
       </c>
       <c r="D80">
-        <v>985.7234217285444</v>
+        <v>956.8998482631666</v>
       </c>
       <c r="E80">
-        <v>292.0370890061824</v>
+        <v>300.9672213240833</v>
       </c>
       <c r="F80">
-        <v>696.5503207962622</v>
+        <v>705.4804531141631</v>
       </c>
       <c r="G80">
         <v>117.5</v>
@@ -7847,45 +7847,45 @@
         <v>162.7875</v>
       </c>
       <c r="M80">
-        <v>40.26060854202396</v>
+        <v>43.2459517758982</v>
       </c>
       <c r="N80">
-        <v>122.526891457976</v>
+        <v>119.5415482241018</v>
       </c>
       <c r="O80">
-        <v>33.08226069365352</v>
+        <v>32.27621802050748</v>
       </c>
       <c r="P80">
-        <v>89.44463076432248</v>
+        <v>87.26533020359429</v>
       </c>
       <c r="Q80">
-        <v>138.2446307643225</v>
+        <v>136.0653302035943</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3259242322013229</v>
+        <v>0.3382597425652501</v>
       </c>
       <c r="T80">
-        <v>3.355816120629962</v>
+        <v>3.503592356231437</v>
       </c>
       <c r="U80">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V80">
         <v>0.27</v>
       </c>
       <c r="W80">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y80">
-        <v>4.043344248760737</v>
+        <v>3.764225165943153</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1063862559387025</v>
+        <v>0.106164960793114</v>
       </c>
       <c r="C81">
-        <v>368.9193951490035</v>
+        <v>363.4972132787276</v>
       </c>
       <c r="D81">
-        <v>956.8998482631666</v>
+        <v>960.4077987107914</v>
       </c>
       <c r="E81">
-        <v>300.9672213240833</v>
+        <v>309.8973536419841</v>
       </c>
       <c r="F81">
-        <v>705.4804531141631</v>
+        <v>714.4105854320638</v>
       </c>
       <c r="G81">
         <v>117.5</v>
@@ -7929,28 +7929,28 @@
         <v>162.7875</v>
       </c>
       <c r="M81">
-        <v>43.2459517758982</v>
+        <v>43.79336888698551</v>
       </c>
       <c r="N81">
-        <v>119.5415482241018</v>
+        <v>118.9941311130144</v>
       </c>
       <c r="O81">
-        <v>32.27621802050748</v>
+        <v>32.1284154005139</v>
       </c>
       <c r="P81">
-        <v>87.26533020359429</v>
+        <v>86.86571571250055</v>
       </c>
       <c r="Q81">
-        <v>136.0653302035943</v>
+        <v>135.6657157125005</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3382597425652501</v>
+        <v>0.35182880396557</v>
       </c>
       <c r="T81">
-        <v>3.503592356231437</v>
+        <v>3.666146215393058</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.764225165943153</v>
+        <v>3.717172351368863</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.106164960793114</v>
+        <v>0.1059436656475254</v>
       </c>
       <c r="C82">
-        <v>363.4972132787276</v>
+        <v>358.1008460107593</v>
       </c>
       <c r="D82">
-        <v>960.4077987107914</v>
+        <v>963.941563760724</v>
       </c>
       <c r="E82">
-        <v>309.8973536419841</v>
+        <v>318.8274859598849</v>
       </c>
       <c r="F82">
-        <v>714.4105854320638</v>
+        <v>723.3407177499647</v>
       </c>
       <c r="G82">
         <v>117.5</v>
@@ -8011,28 +8011,28 @@
         <v>162.7875</v>
       </c>
       <c r="M82">
-        <v>43.79336888698551</v>
+        <v>44.34078599807284</v>
       </c>
       <c r="N82">
-        <v>118.9941311130144</v>
+        <v>118.4467140019271</v>
       </c>
       <c r="O82">
-        <v>32.1284154005139</v>
+        <v>31.98061278052032</v>
       </c>
       <c r="P82">
-        <v>86.86571571250055</v>
+        <v>86.4661012214068</v>
       </c>
       <c r="Q82">
-        <v>135.6657157125005</v>
+        <v>135.2661012214068</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.35182880396557</v>
+        <v>0.3668261876185551</v>
       </c>
       <c r="T82">
-        <v>3.666146215393058</v>
+        <v>3.845811007098007</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.717172351368863</v>
+        <v>3.671281334685296</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1059436656475254</v>
+        <v>0.1057223705019369</v>
       </c>
       <c r="C83">
-        <v>358.1008460107593</v>
+        <v>352.7305793474452</v>
       </c>
       <c r="D83">
-        <v>963.941563760724</v>
+        <v>967.5014294153108</v>
       </c>
       <c r="E83">
-        <v>318.8274859598849</v>
+        <v>327.7576182777857</v>
       </c>
       <c r="F83">
-        <v>723.3407177499647</v>
+        <v>732.2708500678655</v>
       </c>
       <c r="G83">
         <v>117.5</v>
@@ -8093,28 +8093,28 @@
         <v>162.7875</v>
       </c>
       <c r="M83">
-        <v>44.34078599807284</v>
+        <v>44.88820310916015</v>
       </c>
       <c r="N83">
-        <v>118.4467140019271</v>
+        <v>117.8992968908398</v>
       </c>
       <c r="O83">
-        <v>31.98061278052032</v>
+        <v>31.83281016052675</v>
       </c>
       <c r="P83">
-        <v>86.4661012214068</v>
+        <v>86.06648673031307</v>
       </c>
       <c r="Q83">
-        <v>135.2661012214068</v>
+        <v>134.8664867303131</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3668261876185551</v>
+        <v>0.383489947232983</v>
       </c>
       <c r="T83">
-        <v>3.845811007098007</v>
+        <v>4.045438553436841</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.671281334685296</v>
+        <v>3.626509611091574</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1057223705019369</v>
+        <v>0.1055010753563484</v>
       </c>
       <c r="C84">
-        <v>352.7305793474452</v>
+        <v>347.3867035316526</v>
       </c>
       <c r="D84">
-        <v>967.5014294153108</v>
+        <v>971.0876859174189</v>
       </c>
       <c r="E84">
-        <v>327.7576182777857</v>
+        <v>336.6877505956865</v>
       </c>
       <c r="F84">
-        <v>732.2708500678655</v>
+        <v>741.2009823857662</v>
       </c>
       <c r="G84">
         <v>117.5</v>
@@ -8175,28 +8175,28 @@
         <v>162.7875</v>
       </c>
       <c r="M84">
-        <v>44.88820310916015</v>
+        <v>45.43562022024747</v>
       </c>
       <c r="N84">
-        <v>117.8992968908398</v>
+        <v>117.3518797797525</v>
       </c>
       <c r="O84">
-        <v>31.83281016052675</v>
+        <v>31.68500754053317</v>
       </c>
       <c r="P84">
-        <v>86.06648673031307</v>
+        <v>85.66687223921932</v>
       </c>
       <c r="Q84">
-        <v>134.8664867303131</v>
+        <v>134.4668722392193</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.383489947232983</v>
+        <v>0.4021141491549908</v>
       </c>
       <c r="T84">
-        <v>4.045438553436841</v>
+        <v>4.268551693462597</v>
       </c>
       <c r="U84">
         <v>0.0613</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.626509611091574</v>
+        <v>3.582816724210953</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1055010753563484</v>
+        <v>0.1052797802107599</v>
       </c>
       <c r="C85">
-        <v>347.3867035316526</v>
+        <v>342.0695131256563</v>
       </c>
       <c r="D85">
-        <v>971.0876859174189</v>
+        <v>974.7006278293234</v>
       </c>
       <c r="E85">
-        <v>336.6877505956865</v>
+        <v>345.6178829135873</v>
       </c>
       <c r="F85">
-        <v>741.2009823857662</v>
+        <v>750.1311147036671</v>
       </c>
       <c r="G85">
         <v>117.5</v>
@@ -8257,28 +8257,28 @@
         <v>162.7875</v>
       </c>
       <c r="M85">
-        <v>45.43562022024747</v>
+        <v>45.98303733133479</v>
       </c>
       <c r="N85">
-        <v>117.3518797797525</v>
+        <v>116.8044626686652</v>
       </c>
       <c r="O85">
-        <v>31.68500754053317</v>
+        <v>31.5372049205396</v>
       </c>
       <c r="P85">
-        <v>85.66687223921932</v>
+        <v>85.26725774812557</v>
       </c>
       <c r="Q85">
-        <v>134.4668722392193</v>
+        <v>134.0672577481256</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4021141491549908</v>
+        <v>0.4230663763172494</v>
       </c>
       <c r="T85">
-        <v>4.268551693462597</v>
+        <v>4.519553975991572</v>
       </c>
       <c r="U85">
         <v>0.0613</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.582816724210953</v>
+        <v>3.540164144160822</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1052797802107599</v>
+        <v>0.1067958850651713</v>
       </c>
       <c r="C86">
-        <v>342.0695131256564</v>
+        <v>308.9123636594508</v>
       </c>
       <c r="D86">
-        <v>974.7006278293234</v>
+        <v>950.4736106810185</v>
       </c>
       <c r="E86">
-        <v>345.6178829135872</v>
+        <v>354.548015231488</v>
       </c>
       <c r="F86">
-        <v>750.131114703667</v>
+        <v>759.0612470215677</v>
       </c>
       <c r="G86">
         <v>117.5</v>
@@ -8339,45 +8339,45 @@
         <v>162.7875</v>
       </c>
       <c r="M86">
-        <v>45.98303733133478</v>
+        <v>48.65582593408249</v>
       </c>
       <c r="N86">
-        <v>116.8044626686652</v>
+        <v>114.1316740659175</v>
       </c>
       <c r="O86">
-        <v>31.5372049205396</v>
+        <v>30.81555199779772</v>
       </c>
       <c r="P86">
-        <v>85.26725774812559</v>
+        <v>83.31612206811975</v>
       </c>
       <c r="Q86">
-        <v>134.0672577481256</v>
+        <v>132.1161220681198</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4230663763172491</v>
+        <v>0.4468122337678089</v>
       </c>
       <c r="T86">
-        <v>4.519553975991569</v>
+        <v>4.804023229524406</v>
       </c>
       <c r="U86">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V86">
         <v>0.27</v>
       </c>
       <c r="W86">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y86">
-        <v>3.540164144160823</v>
+        <v>3.345693899442582</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1067958850651713</v>
+        <v>0.1065950299195828</v>
       </c>
       <c r="C87">
-        <v>308.9123636594508</v>
+        <v>303.122414275976</v>
       </c>
       <c r="D87">
-        <v>950.4736106810185</v>
+        <v>953.6137936154446</v>
       </c>
       <c r="E87">
-        <v>354.548015231488</v>
+        <v>363.4781475493888</v>
       </c>
       <c r="F87">
-        <v>759.0612470215677</v>
+        <v>767.9913793394686</v>
       </c>
       <c r="G87">
         <v>117.5</v>
@@ -8421,28 +8421,28 @@
         <v>162.7875</v>
       </c>
       <c r="M87">
-        <v>48.65582593408249</v>
+        <v>49.22824741565994</v>
       </c>
       <c r="N87">
-        <v>114.1316740659175</v>
+        <v>113.55925258434</v>
       </c>
       <c r="O87">
-        <v>30.81555199779772</v>
+        <v>30.66099819777181</v>
       </c>
       <c r="P87">
-        <v>83.31612206811975</v>
+        <v>82.89825438656821</v>
       </c>
       <c r="Q87">
-        <v>132.1161220681198</v>
+        <v>131.6982543865682</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4468122337678089</v>
+        <v>0.4739503565684486</v>
       </c>
       <c r="T87">
-        <v>4.804023229524406</v>
+        <v>5.129130947847648</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.345693899442582</v>
+        <v>3.306790482007202</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1065950299195828</v>
+        <v>0.1063941747739943</v>
       </c>
       <c r="C88">
-        <v>303.122414275976</v>
+        <v>297.3532827979459</v>
       </c>
       <c r="D88">
-        <v>953.6137936154446</v>
+        <v>956.7747944553154</v>
       </c>
       <c r="E88">
-        <v>363.4781475493888</v>
+        <v>372.4082798672896</v>
       </c>
       <c r="F88">
-        <v>767.9913793394686</v>
+        <v>776.9215116573694</v>
       </c>
       <c r="G88">
         <v>117.5</v>
@@ -8503,28 +8503,28 @@
         <v>162.7875</v>
       </c>
       <c r="M88">
-        <v>49.22824741565994</v>
+        <v>49.80066889723738</v>
       </c>
       <c r="N88">
-        <v>113.55925258434</v>
+        <v>112.9868311027626</v>
       </c>
       <c r="O88">
-        <v>30.66099819777181</v>
+        <v>30.5064443977459</v>
       </c>
       <c r="P88">
-        <v>82.89825438656821</v>
+        <v>82.48038670501668</v>
       </c>
       <c r="Q88">
-        <v>131.6982543865682</v>
+        <v>131.2803867050167</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4739503565684486</v>
+        <v>0.5052635751845712</v>
       </c>
       <c r="T88">
-        <v>5.129130947847648</v>
+        <v>5.50425523822062</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.306790482007202</v>
+        <v>3.26878139600712</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1063941747739943</v>
+        <v>0.1061933196284057</v>
       </c>
       <c r="C89">
-        <v>297.3532827979459</v>
+        <v>291.6051769329406</v>
       </c>
       <c r="D89">
-        <v>956.7747944553154</v>
+        <v>959.9568209082109</v>
       </c>
       <c r="E89">
-        <v>372.4082798672896</v>
+        <v>381.3384121851905</v>
       </c>
       <c r="F89">
-        <v>776.9215116573694</v>
+        <v>785.8516439752702</v>
       </c>
       <c r="G89">
         <v>117.5</v>
@@ -8585,28 +8585,28 @@
         <v>162.7875</v>
       </c>
       <c r="M89">
-        <v>49.80066889723738</v>
+        <v>50.37309037881482</v>
       </c>
       <c r="N89">
-        <v>112.9868311027626</v>
+        <v>112.4144096211851</v>
       </c>
       <c r="O89">
-        <v>30.5064443977459</v>
+        <v>30.35189059771999</v>
       </c>
       <c r="P89">
-        <v>82.48038670501668</v>
+        <v>82.06251902346516</v>
       </c>
       <c r="Q89">
-        <v>131.2803867050167</v>
+        <v>130.8625190234652</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5052635751845712</v>
+        <v>0.5417956635700478</v>
       </c>
       <c r="T89">
-        <v>5.50425523822062</v>
+        <v>5.941900243655755</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.26878139600712</v>
+        <v>3.231636152870675</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1061933196284057</v>
+        <v>0.1059924644828172</v>
       </c>
       <c r="C90">
-        <v>291.6051769329406</v>
+        <v>285.8783071609231</v>
       </c>
       <c r="D90">
-        <v>959.9568209082109</v>
+        <v>963.1600834540942</v>
       </c>
       <c r="E90">
-        <v>381.3384121851905</v>
+        <v>390.2685445030912</v>
       </c>
       <c r="F90">
-        <v>785.8516439752702</v>
+        <v>794.781776293171</v>
       </c>
       <c r="G90">
         <v>117.5</v>
@@ -8667,28 +8667,28 @@
         <v>162.7875</v>
       </c>
       <c r="M90">
-        <v>50.37309037881482</v>
+        <v>50.94551186039227</v>
       </c>
       <c r="N90">
-        <v>112.4144096211851</v>
+        <v>111.8419881396077</v>
       </c>
       <c r="O90">
-        <v>30.35189059771999</v>
+        <v>30.19733679769408</v>
       </c>
       <c r="P90">
-        <v>82.06251902346516</v>
+        <v>81.64465134191363</v>
       </c>
       <c r="Q90">
-        <v>130.8625190234652</v>
+        <v>130.4446513419136</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5417956635700478</v>
+        <v>0.5849699498437928</v>
       </c>
       <c r="T90">
-        <v>5.941900243655755</v>
+        <v>6.459117068260913</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.231636152870675</v>
+        <v>3.195325634299095</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1059924644828172</v>
+        <v>0.1057916093372287</v>
       </c>
       <c r="C91">
-        <v>285.8783071609231</v>
+        <v>280.1728867806493</v>
       </c>
       <c r="D91">
-        <v>963.1600834540942</v>
+        <v>966.3847953917212</v>
       </c>
       <c r="E91">
-        <v>390.2685445030912</v>
+        <v>399.1986768209921</v>
       </c>
       <c r="F91">
-        <v>794.781776293171</v>
+        <v>803.7119086110719</v>
       </c>
       <c r="G91">
         <v>117.5</v>
@@ -8749,28 +8749,28 @@
         <v>162.7875</v>
       </c>
       <c r="M91">
-        <v>50.94551186039227</v>
+        <v>51.51793334196971</v>
       </c>
       <c r="N91">
-        <v>111.8419881396077</v>
+        <v>111.2695666580303</v>
       </c>
       <c r="O91">
-        <v>30.19733679769408</v>
+        <v>30.04278299766817</v>
       </c>
       <c r="P91">
-        <v>81.64465134191363</v>
+        <v>81.22678366036209</v>
       </c>
       <c r="Q91">
-        <v>130.4446513419136</v>
+        <v>130.0267836603621</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5849699498437928</v>
+        <v>0.6367790933722869</v>
       </c>
       <c r="T91">
-        <v>6.459117068260913</v>
+        <v>7.079777257787105</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.195325634299095</v>
+        <v>3.159822016140216</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1057916093372287</v>
+        <v>0.1055907541916402</v>
       </c>
       <c r="C92">
-        <v>280.1728867806493</v>
+        <v>274.4891319570147</v>
       </c>
       <c r="D92">
-        <v>966.3847953917212</v>
+        <v>969.6311728859874</v>
       </c>
       <c r="E92">
-        <v>399.1986768209921</v>
+        <v>408.1288091388928</v>
       </c>
       <c r="F92">
-        <v>803.7119086110719</v>
+        <v>812.6420409289726</v>
       </c>
       <c r="G92">
         <v>117.5</v>
@@ -8831,28 +8831,28 @@
         <v>162.7875</v>
       </c>
       <c r="M92">
-        <v>51.51793334196971</v>
+        <v>52.09035482354715</v>
       </c>
       <c r="N92">
-        <v>111.2695666580303</v>
+        <v>110.6971451764528</v>
       </c>
       <c r="O92">
-        <v>30.04278299766817</v>
+        <v>29.88822919764226</v>
       </c>
       <c r="P92">
-        <v>81.22678366036209</v>
+        <v>80.80891597881055</v>
       </c>
       <c r="Q92">
-        <v>130.0267836603621</v>
+        <v>129.6089159788106</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6367790933722869</v>
+        <v>0.700101379907113</v>
       </c>
       <c r="T92">
-        <v>7.079777257787105</v>
+        <v>7.838361933874672</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.159822016140216</v>
+        <v>3.125098697281532</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1055907541916402</v>
+        <v>0.1053898990460516</v>
       </c>
       <c r="C93">
-        <v>274.4891319570147</v>
+        <v>268.8272617693568</v>
       </c>
       <c r="D93">
-        <v>969.6311728859874</v>
+        <v>972.8994350162303</v>
       </c>
       <c r="E93">
-        <v>408.1288091388928</v>
+        <v>417.0589414567936</v>
       </c>
       <c r="F93">
-        <v>812.6420409289726</v>
+        <v>821.5721732468734</v>
       </c>
       <c r="G93">
         <v>117.5</v>
@@ -8913,28 +8913,28 @@
         <v>162.7875</v>
       </c>
       <c r="M93">
-        <v>52.09035482354715</v>
+        <v>52.66277630512459</v>
       </c>
       <c r="N93">
-        <v>110.6971451764528</v>
+        <v>110.1247236948754</v>
       </c>
       <c r="O93">
-        <v>29.88822919764226</v>
+        <v>29.73367539761635</v>
       </c>
       <c r="P93">
-        <v>80.80891597881055</v>
+        <v>80.39104829725902</v>
       </c>
       <c r="Q93">
-        <v>129.6089159788106</v>
+        <v>129.191048297259</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.700101379907113</v>
+        <v>0.7792542380756456</v>
       </c>
       <c r="T93">
-        <v>7.838361933874672</v>
+        <v>8.786592778984131</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.125098697281532</v>
+        <v>3.091130233180646</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1053898990460516</v>
+        <v>0.1051890439004631</v>
       </c>
       <c r="C94">
-        <v>268.8272617693568</v>
+        <v>263.1874982607379</v>
       </c>
       <c r="D94">
-        <v>972.8994350162303</v>
+        <v>976.1898038255123</v>
       </c>
       <c r="E94">
-        <v>417.0589414567936</v>
+        <v>425.9890737746945</v>
       </c>
       <c r="F94">
-        <v>821.5721732468734</v>
+        <v>830.5023055647742</v>
       </c>
       <c r="G94">
         <v>117.5</v>
@@ -8995,28 +8995,28 @@
         <v>162.7875</v>
       </c>
       <c r="M94">
-        <v>52.66277630512459</v>
+        <v>53.23519778670203</v>
       </c>
       <c r="N94">
-        <v>110.1247236948754</v>
+        <v>109.5523022132979</v>
       </c>
       <c r="O94">
-        <v>29.73367539761635</v>
+        <v>29.57912159759044</v>
       </c>
       <c r="P94">
-        <v>80.39104829725902</v>
+        <v>79.97318061570749</v>
       </c>
       <c r="Q94">
-        <v>129.191048297259</v>
+        <v>128.7731806157075</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7792542380756456</v>
+        <v>0.8810221985780448</v>
       </c>
       <c r="T94">
-        <v>8.786592778984131</v>
+        <v>10.00574672269629</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.091130233180646</v>
+        <v>3.05789227368408</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1051890439004631</v>
+        <v>0.1049881887548746</v>
       </c>
       <c r="C95">
-        <v>263.1874982607379</v>
+        <v>257.5700664882356</v>
       </c>
       <c r="D95">
-        <v>976.1898038255123</v>
+        <v>979.5025043709107</v>
       </c>
       <c r="E95">
-        <v>425.9890737746945</v>
+        <v>434.9192060925952</v>
       </c>
       <c r="F95">
-        <v>830.5023055647742</v>
+        <v>839.432437882675</v>
       </c>
       <c r="G95">
         <v>117.5</v>
@@ -9077,28 +9077,28 @@
         <v>162.7875</v>
       </c>
       <c r="M95">
-        <v>53.23519778670203</v>
+        <v>53.80761926827947</v>
       </c>
       <c r="N95">
-        <v>109.5523022132979</v>
+        <v>108.9798807317205</v>
       </c>
       <c r="O95">
-        <v>29.57912159759044</v>
+        <v>29.42456779756453</v>
       </c>
       <c r="P95">
-        <v>79.97318061570749</v>
+        <v>79.55531293415596</v>
       </c>
       <c r="Q95">
-        <v>128.7731806157075</v>
+        <v>128.355312934156</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8810221985780448</v>
+        <v>1.016712812581244</v>
       </c>
       <c r="T95">
-        <v>10.00574672269629</v>
+        <v>11.63128531431251</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.05789227368408</v>
+        <v>3.0253615048151</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1049881887548746</v>
+        <v>0.110196633609286</v>
       </c>
       <c r="C96">
-        <v>257.5700664882356</v>
+        <v>169.4170851977116</v>
       </c>
       <c r="D96">
-        <v>979.5025043709107</v>
+        <v>900.2796553982874</v>
       </c>
       <c r="E96">
-        <v>434.9192060925952</v>
+        <v>443.8493384104961</v>
       </c>
       <c r="F96">
-        <v>839.432437882675</v>
+        <v>848.3625702005759</v>
       </c>
       <c r="G96">
         <v>117.5</v>
@@ -9159,45 +9159,45 @@
         <v>162.7875</v>
       </c>
       <c r="M96">
-        <v>53.80761926827947</v>
+        <v>60.99726879742141</v>
       </c>
       <c r="N96">
-        <v>108.9798807317205</v>
+        <v>101.7902312025786</v>
       </c>
       <c r="O96">
-        <v>29.42456779756453</v>
+        <v>27.48336242469621</v>
       </c>
       <c r="P96">
-        <v>79.55531293415596</v>
+        <v>74.30686877788234</v>
       </c>
       <c r="Q96">
-        <v>128.355312934156</v>
+        <v>123.1068687778823</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.016712812581244</v>
+        <v>1.206679672185722</v>
       </c>
       <c r="T96">
-        <v>11.63128531431251</v>
+        <v>13.90703934257521</v>
       </c>
       <c r="U96">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V96">
         <v>0.27</v>
       </c>
       <c r="W96">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y96">
-        <v>3.0253615048151</v>
+        <v>2.668767031859001</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.110196633609286</v>
+        <v>0.1100527184636975</v>
       </c>
       <c r="C97">
-        <v>169.4170851977116</v>
+        <v>162.5034259688096</v>
       </c>
       <c r="D97">
-        <v>900.2796553982874</v>
+        <v>902.2961284872862</v>
       </c>
       <c r="E97">
-        <v>443.8493384104961</v>
+        <v>452.7794707283969</v>
       </c>
       <c r="F97">
-        <v>848.3625702005759</v>
+        <v>857.2927025184766</v>
       </c>
       <c r="G97">
         <v>117.5</v>
@@ -9241,28 +9241,28 @@
         <v>162.7875</v>
       </c>
       <c r="M97">
-        <v>60.99726879742141</v>
+        <v>61.63934531107847</v>
       </c>
       <c r="N97">
-        <v>101.7902312025786</v>
+        <v>101.1481546889215</v>
       </c>
       <c r="O97">
-        <v>27.48336242469621</v>
+        <v>27.31000176600881</v>
       </c>
       <c r="P97">
-        <v>74.30686877788234</v>
+        <v>73.83815292291268</v>
       </c>
       <c r="Q97">
-        <v>123.1068687778823</v>
+        <v>122.6381529229127</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.206679672185722</v>
+        <v>1.49162996159244</v>
       </c>
       <c r="T97">
-        <v>13.90703934257521</v>
+        <v>17.32067038496927</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.668767031859001</v>
+        <v>2.640967375277136</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1100527184636975</v>
+        <v>0.109908803318109</v>
       </c>
       <c r="C98">
-        <v>162.5034259688092</v>
+        <v>155.5988201304915</v>
       </c>
       <c r="D98">
-        <v>902.2961284872857</v>
+        <v>904.3216549668689</v>
       </c>
       <c r="E98">
-        <v>452.7794707283967</v>
+        <v>461.7096030462976</v>
       </c>
       <c r="F98">
-        <v>857.2927025184765</v>
+        <v>866.2228348363774</v>
       </c>
       <c r="G98">
         <v>117.5</v>
@@ -9323,28 +9323,28 @@
         <v>162.7875</v>
       </c>
       <c r="M98">
-        <v>61.63934531107846</v>
+        <v>62.28142182473554</v>
       </c>
       <c r="N98">
-        <v>101.1481546889215</v>
+        <v>100.5060781752644</v>
       </c>
       <c r="O98">
-        <v>27.31000176600881</v>
+        <v>27.1366411073214</v>
       </c>
       <c r="P98">
-        <v>73.83815292291268</v>
+        <v>73.36943706794304</v>
       </c>
       <c r="Q98">
-        <v>122.6381529229127</v>
+        <v>122.169437067943</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.491629961592436</v>
+        <v>1.966547110603631</v>
       </c>
       <c r="T98">
-        <v>17.32067038496923</v>
+        <v>23.01005545562597</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.640967375277136</v>
+        <v>2.613740907490774</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.109908803318109</v>
+        <v>0.1097648881725204</v>
       </c>
       <c r="C99">
-        <v>155.5988201304915</v>
+        <v>148.70332879066</v>
       </c>
       <c r="D99">
-        <v>904.3216549668689</v>
+        <v>906.3562959449381</v>
       </c>
       <c r="E99">
-        <v>461.7096030462976</v>
+        <v>470.6397353641984</v>
       </c>
       <c r="F99">
-        <v>866.2228348363774</v>
+        <v>875.1529671542781</v>
       </c>
       <c r="G99">
         <v>117.5</v>
@@ -9405,28 +9405,28 @@
         <v>162.7875</v>
       </c>
       <c r="M99">
-        <v>62.28142182473554</v>
+        <v>62.9234983383926</v>
       </c>
       <c r="N99">
-        <v>100.5060781752644</v>
+        <v>99.86400166160736</v>
       </c>
       <c r="O99">
-        <v>27.1366411073214</v>
+        <v>26.96328044863399</v>
       </c>
       <c r="P99">
-        <v>73.36943706794304</v>
+        <v>72.90072121297337</v>
       </c>
       <c r="Q99">
-        <v>122.169437067943</v>
+        <v>121.7007212129734</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.966547110603631</v>
+        <v>2.91638140862602</v>
       </c>
       <c r="T99">
-        <v>23.01005545562597</v>
+        <v>34.38882559693944</v>
       </c>
       <c r="U99">
         <v>0.07190000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.613740907490774</v>
+        <v>2.587070081904133</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1097648881725204</v>
+        <v>0.1096209730269319</v>
       </c>
       <c r="C100">
-        <v>148.70332879066</v>
+        <v>141.8170136084044</v>
       </c>
       <c r="D100">
-        <v>906.3562959449381</v>
+        <v>908.4001130805834</v>
       </c>
       <c r="E100">
-        <v>470.6397353641984</v>
+        <v>479.5698676820992</v>
       </c>
       <c r="F100">
-        <v>875.1529671542781</v>
+        <v>884.083099472179</v>
       </c>
       <c r="G100">
         <v>117.5</v>
@@ -9487,28 +9487,28 @@
         <v>162.7875</v>
       </c>
       <c r="M100">
-        <v>62.9234983383926</v>
+        <v>63.56557485204968</v>
       </c>
       <c r="N100">
-        <v>99.86400166160736</v>
+        <v>99.22192514795029</v>
       </c>
       <c r="O100">
-        <v>26.96328044863399</v>
+        <v>26.78991978994658</v>
       </c>
       <c r="P100">
-        <v>72.90072121297337</v>
+        <v>72.43200535800371</v>
       </c>
       <c r="Q100">
-        <v>121.7007212129734</v>
+        <v>121.2320053580037</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.91638140862602</v>
+        <v>5.765884302693186</v>
       </c>
       <c r="T100">
-        <v>34.38882559693944</v>
+        <v>68.52513602087987</v>
       </c>
       <c r="U100">
         <v>0.07190000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.587070081904133</v>
+        <v>2.560938060874799</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1096209730269319</v>
-      </c>
-      <c r="C101">
-        <v>141.8170136084044</v>
-      </c>
-      <c r="D101">
-        <v>908.4001130805834</v>
-      </c>
-      <c r="E101">
-        <v>479.5698676820992</v>
-      </c>
-      <c r="F101">
-        <v>884.083099472179</v>
-      </c>
-      <c r="G101">
-        <v>117.5</v>
-      </c>
-      <c r="H101">
-        <v>488.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>211.5875</v>
-      </c>
-      <c r="K101">
-        <v>48.8</v>
-      </c>
-      <c r="L101">
-        <v>162.7875</v>
-      </c>
-      <c r="M101">
-        <v>63.56557485204968</v>
-      </c>
-      <c r="N101">
-        <v>99.22192514795029</v>
-      </c>
-      <c r="O101">
-        <v>26.78991978994658</v>
-      </c>
-      <c r="P101">
-        <v>72.43200535800371</v>
-      </c>
-      <c r="Q101">
-        <v>121.2320053580037</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.765884302693186</v>
-      </c>
-      <c r="T101">
-        <v>68.52513602087987</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.27</v>
-      </c>
-      <c r="W101">
-        <v>0.05248700000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.560938060874799</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
